--- a/docs/HMS_TestCases.xlsx
+++ b/docs/HMS_TestCases.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\HOC_TAP\QL-KhachSan\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59C365AD-8027-466D-8814-03CF7AF91E4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF039AA3-DEEE-425D-A8B9-05D5154DADDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4680" yWindow="2250" windowWidth="21600" windowHeight="11835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="2250" windowWidth="21600" windowHeight="11835" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AUTH" sheetId="1" r:id="rId1"/>
@@ -19,10 +19,9 @@
     <sheet name="CHECKIN" sheetId="4" r:id="rId4"/>
     <sheet name="PAYMENT" sheetId="5" r:id="rId5"/>
     <sheet name="CUSTOMER" sheetId="6" r:id="rId6"/>
-    <sheet name="EDGE" sheetId="7" r:id="rId7"/>
-    <sheet name="PERFORMANCE" sheetId="8" r:id="rId8"/>
-    <sheet name="SECURITY" sheetId="9" r:id="rId9"/>
-    <sheet name="REGRESSION" sheetId="10" r:id="rId10"/>
+    <sheet name="REVIEW" sheetId="11" r:id="rId7"/>
+    <sheet name="SECURITY" sheetId="9" r:id="rId8"/>
+    <sheet name="REGRESSION" sheetId="10" r:id="rId9"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -34,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="286">
   <si>
     <t>TC_ID</t>
   </si>
@@ -60,58 +59,15 @@
     <t>AUTH01</t>
   </si>
   <si>
-    <t>Login hợp lệ</t>
-  </si>
-  <si>
-    <t>User tồn tại</t>
-  </si>
-  <si>
-    <t>1. Mở trang login
-2. Nhập email &amp; password
-3. Submit</t>
-  </si>
-  <si>
-    <t>email=user@test.com; password=123456</t>
-  </si>
-  <si>
-    <t>Đăng nhập thành công, trả về token</t>
-  </si>
-  <si>
     <t>AUTH02</t>
   </si>
   <si>
-    <t>Sai mật khẩu</t>
-  </si>
-  <si>
-    <t>1. Nhập email đúng, password sai
-2. Submit</t>
-  </si>
-  <si>
-    <t>password=wrong</t>
-  </si>
-  <si>
-    <t>Hiển thị lỗi xác thực</t>
-  </si>
-  <si>
     <t>AUTH03</t>
   </si>
   <si>
     <t>Email không tồn tại</t>
   </si>
   <si>
-    <t>Không có user</t>
-  </si>
-  <si>
-    <t>1. Nhập email không tồn tại
-2. Submit</t>
-  </si>
-  <si>
-    <t>email=none@test.com</t>
-  </si>
-  <si>
-    <t>Hiển thị lỗi</t>
-  </si>
-  <si>
     <t>AUTH04</t>
   </si>
   <si>
@@ -121,31 +77,12 @@
     <t>-</t>
   </si>
   <si>
-    <t>1. Để trống password
-2. Submit</t>
-  </si>
-  <si>
     <t>password=null</t>
   </si>
   <si>
-    <t>400 Bad Request</t>
-  </si>
-  <si>
     <t>AUTH05</t>
   </si>
   <si>
-    <t>JWT hết hạn</t>
-  </si>
-  <si>
-    <t>Đã login trước đó</t>
-  </si>
-  <si>
-    <t>1. Gọi API với token hết hạn</t>
-  </si>
-  <si>
-    <t>expired_token</t>
-  </si>
-  <si>
     <t>401 Unauthorized</t>
   </si>
   <si>
@@ -440,153 +377,12 @@
     <t>duplicate</t>
   </si>
   <si>
-    <t>CUS01</t>
-  </si>
-  <si>
-    <t>Customer</t>
-  </si>
-  <si>
-    <t>Thêm khách</t>
-  </si>
-  <si>
-    <t>1. POST /customers</t>
-  </si>
-  <si>
-    <t>name, phone</t>
-  </si>
-  <si>
-    <t>CUS02</t>
-  </si>
-  <si>
-    <t>Thiếu tên</t>
-  </si>
-  <si>
-    <t>1. POST thiếu name</t>
-  </si>
-  <si>
-    <t>CUS03</t>
-  </si>
-  <si>
-    <t>SĐT sai</t>
-  </si>
-  <si>
-    <t>1. POST phone sai</t>
-  </si>
-  <si>
-    <t>phone=abc</t>
-  </si>
-  <si>
-    <t>CUS04</t>
-  </si>
-  <si>
-    <t>Danh sách</t>
-  </si>
-  <si>
-    <t>1. GET /customers</t>
-  </si>
-  <si>
-    <t>Trả về danh sách</t>
-  </si>
-  <si>
-    <t>EDGE01</t>
-  </si>
-  <si>
-    <t>Edge</t>
-  </si>
-  <si>
-    <t>Race condition booking</t>
-  </si>
-  <si>
-    <t>2 user đồng thời</t>
-  </si>
-  <si>
-    <t>1. Gửi 2 request cùng lúc</t>
-  </si>
-  <si>
-    <t>same room</t>
-  </si>
-  <si>
-    <t>Chỉ 1 booking thành công</t>
-  </si>
-  <si>
-    <t>EDGE02</t>
-  </si>
-  <si>
-    <t>Dữ liệu lớn</t>
-  </si>
-  <si>
-    <t>1. Gửi payload lớn</t>
-  </si>
-  <si>
-    <t>large data</t>
-  </si>
-  <si>
-    <t>Không crash</t>
-  </si>
-  <si>
-    <t>Performance</t>
-  </si>
-  <si>
-    <t>EDGE03</t>
-  </si>
-  <si>
-    <t>SQL injection</t>
-  </si>
-  <si>
-    <t>1. Input độc hại</t>
-  </si>
-  <si>
-    <t>' OR 1=1</t>
-  </si>
-  <si>
-    <t>Bị chặn</t>
-  </si>
-  <si>
-    <t>EDGE04</t>
-  </si>
-  <si>
     <t>Token hết hạn</t>
   </si>
   <si>
-    <t>1. Gọi API với token cũ</t>
-  </si>
-  <si>
-    <t>expired</t>
-  </si>
-  <si>
     <t>401</t>
   </si>
   <si>
-    <t>PERF01</t>
-  </si>
-  <si>
-    <t>100 user đồng thời</t>
-  </si>
-  <si>
-    <t>1. Load test</t>
-  </si>
-  <si>
-    <t>100 users</t>
-  </si>
-  <si>
-    <t>Hệ thống ổn định</t>
-  </si>
-  <si>
-    <t>PERF02</t>
-  </si>
-  <si>
-    <t>Query lớn</t>
-  </si>
-  <si>
-    <t>1. Query nhiều data</t>
-  </si>
-  <si>
-    <t>large DB</t>
-  </si>
-  <si>
-    <t>&lt;2s</t>
-  </si>
-  <si>
     <t>SEC01</t>
   </si>
   <si>
@@ -639,13 +435,469 @@
   </si>
   <si>
     <t>Auth</t>
+  </si>
+  <si>
+    <t>REV06</t>
+  </si>
+  <si>
+    <t>Review</t>
+  </si>
+  <si>
+    <t>Lấy booking có thể review</t>
+  </si>
+  <si>
+    <t>User đã đăng nhập</t>
+  </si>
+  <si>
+    <t>1. GET /reviews/my-bookings</t>
+  </si>
+  <si>
+    <t>Trả về danh sách booking</t>
+  </si>
+  <si>
+    <t>REV07</t>
+  </si>
+  <si>
+    <t>Không đăng nhập</t>
+  </si>
+  <si>
+    <t>REV01</t>
+  </si>
+  <si>
+    <t>Tạo review thành công</t>
+  </si>
+  <si>
+    <t>1. POST /reviews</t>
+  </si>
+  <si>
+    <t>rating=5, comment="Good", bookingId=1</t>
+  </si>
+  <si>
+    <t>REV02</t>
+  </si>
+  <si>
+    <t>Thiếu rating</t>
+  </si>
+  <si>
+    <t>rating=null</t>
+  </si>
+  <si>
+    <t>REV03</t>
+  </si>
+  <si>
+    <t>Rating không hợp lệ</t>
+  </si>
+  <si>
+    <t>rating=10</t>
+  </si>
+  <si>
+    <t>REV04</t>
+  </si>
+  <si>
+    <t>Thiếu bookingId</t>
+  </si>
+  <si>
+    <t>bookingId=null</t>
+  </si>
+  <si>
+    <t>REV05</t>
+  </si>
+  <si>
+    <t>Comment rỗng</t>
+  </si>
+  <si>
+    <t>comment=""</t>
+  </si>
+  <si>
+    <t>Thành công (nếu cho phép)</t>
+  </si>
+  <si>
+    <t>REV08</t>
+  </si>
+  <si>
+    <t>Lấy review của user</t>
+  </si>
+  <si>
+    <t>1. GET /reviews/my-reviews</t>
+  </si>
+  <si>
+    <t>Trả về danh sách review</t>
+  </si>
+  <si>
+    <t>REV09</t>
+  </si>
+  <si>
+    <t>Không có review</t>
+  </si>
+  <si>
+    <t>Danh sách rỗng</t>
+  </si>
+  <si>
+    <t>REV10</t>
+  </si>
+  <si>
+    <t>REV11</t>
+  </si>
+  <si>
+    <t>Lấy review theo hotelId</t>
+  </si>
+  <si>
+    <t>Hệ thống có dữ liệu</t>
+  </si>
+  <si>
+    <t>1. GET /reviews/hotel/{id}</t>
+  </si>
+  <si>
+    <t>hotelId=1</t>
+  </si>
+  <si>
+    <t>REV12</t>
+  </si>
+  <si>
+    <t>Hotel không tồn tại</t>
+  </si>
+  <si>
+    <t>hotelId=999</t>
+  </si>
+  <si>
+    <t>Lỗi hoặc rỗng</t>
+  </si>
+  <si>
+    <t>REV13</t>
+  </si>
+  <si>
+    <t>Lấy rating trung bình</t>
+  </si>
+  <si>
+    <t>Hệ thống có review</t>
+  </si>
+  <si>
+    <t>1. GET /reviews/hotel/{id}/rating</t>
+  </si>
+  <si>
+    <t>Trả về số rating</t>
+  </si>
+  <si>
+    <t>REV14</t>
+  </si>
+  <si>
+    <t>Hotel chưa có review</t>
+  </si>
+  <si>
+    <t>hotelId=2</t>
+  </si>
+  <si>
+    <t>Trả về 0 hoặc null</t>
+  </si>
+  <si>
+    <t>REV15</t>
+  </si>
+  <si>
+    <t>Xóa review thành công</t>
+  </si>
+  <si>
+    <t>User là owner</t>
+  </si>
+  <si>
+    <t>1. DELETE /reviews/{id}</t>
+  </si>
+  <si>
+    <t>REV16</t>
+  </si>
+  <si>
+    <t>Xóa review không phải của mình</t>
+  </si>
+  <si>
+    <t>id=2</t>
+  </si>
+  <si>
+    <t>403 Forbidden</t>
+  </si>
+  <si>
+    <t>REV17</t>
+  </si>
+  <si>
+    <t>Xóa review không tồn tại</t>
+  </si>
+  <si>
+    <t>REV18</t>
+  </si>
+  <si>
+    <t>Đăng ký thành công</t>
+  </si>
+  <si>
+    <t>1. POST /auth/register</t>
+  </si>
+  <si>
+    <t>email, password hợp lệ</t>
+  </si>
+  <si>
+    <t>Thiếu email</t>
+  </si>
+  <si>
+    <t>email=null</t>
+  </si>
+  <si>
+    <t>Email sai format</t>
+  </si>
+  <si>
+    <t>email=abc</t>
+  </si>
+  <si>
+    <t>Email đã tồn tại</t>
+  </si>
+  <si>
+    <t>email trùng</t>
+  </si>
+  <si>
+    <t>AUTH06</t>
+  </si>
+  <si>
+    <t>Đăng nhập thành công</t>
+  </si>
+  <si>
+    <t>User đã tồn tại</t>
+  </si>
+  <si>
+    <t>1. POST /auth/login</t>
+  </si>
+  <si>
+    <t>email, password đúng</t>
+  </si>
+  <si>
+    <t>Trả về accessToken + refreshToken</t>
+  </si>
+  <si>
+    <t>AUTH07</t>
+  </si>
+  <si>
+    <t>Sai password</t>
+  </si>
+  <si>
+    <t>password sai</t>
+  </si>
+  <si>
+    <t>AUTH08</t>
+  </si>
+  <si>
+    <t>email=abc@gmail.com</t>
+  </si>
+  <si>
+    <t>AUTH09</t>
+  </si>
+  <si>
+    <t>Thiếu dữ liệu</t>
+  </si>
+  <si>
+    <t>AUTH10</t>
+  </si>
+  <si>
+    <t>Refresh token thành công</t>
+  </si>
+  <si>
+    <t>Có refreshToken</t>
+  </si>
+  <si>
+    <t>1. POST /auth/refresh</t>
+  </si>
+  <si>
+    <t>refreshToken hợp lệ</t>
+  </si>
+  <si>
+    <t>Trả về accessToken mới</t>
+  </si>
+  <si>
+    <t>AUTH11</t>
+  </si>
+  <si>
+    <t>Refresh token không hợp lệ</t>
+  </si>
+  <si>
+    <t>refreshToken sai</t>
+  </si>
+  <si>
+    <t>AUTH12</t>
+  </si>
+  <si>
+    <t>Không có refreshToken</t>
+  </si>
+  <si>
+    <t>refreshToken=null</t>
+  </si>
+  <si>
+    <t>CUSP01</t>
+  </si>
+  <si>
+    <t>Profile</t>
+  </si>
+  <si>
+    <t>Lấy thông tin profile</t>
+  </si>
+  <si>
+    <t>1. GET /profile</t>
+  </si>
+  <si>
+    <t>Trả về thông tin user</t>
+  </si>
+  <si>
+    <t>CUSP02</t>
+  </si>
+  <si>
+    <t>Chưa đăng nhập</t>
+  </si>
+  <si>
+    <t>CUSP03</t>
+  </si>
+  <si>
+    <t>Cập nhật profile thành công</t>
+  </si>
+  <si>
+    <t>1. PUT /profile</t>
+  </si>
+  <si>
+    <t>name="Duy", phone="0123456789"</t>
+  </si>
+  <si>
+    <t>CUSP04</t>
+  </si>
+  <si>
+    <t>Thiếu name</t>
+  </si>
+  <si>
+    <t>CUSP05</t>
+  </si>
+  <si>
+    <t>SĐT sai format</t>
+  </si>
+  <si>
+    <t>phone="abc"</t>
+  </si>
+  <si>
+    <t>CUSP06</t>
+  </si>
+  <si>
+    <t>Dữ liệu rỗng</t>
+  </si>
+  <si>
+    <t>{}</t>
+  </si>
+  <si>
+    <t>Không thay đổi hoặc lỗi validation</t>
+  </si>
+  <si>
+    <t>CUSP07</t>
+  </si>
+  <si>
+    <t>name="Duy"</t>
+  </si>
+  <si>
+    <t>CUSP08</t>
+  </si>
+  <si>
+    <t>Đổi mật khẩu thành công</t>
+  </si>
+  <si>
+    <t>1. PUT /profile/password</t>
+  </si>
+  <si>
+    <t>oldPassword đúng, newPassword hợp lệ</t>
+  </si>
+  <si>
+    <t>CUSP09</t>
+  </si>
+  <si>
+    <t>Sai mật khẩu cũ</t>
+  </si>
+  <si>
+    <t>oldPassword sai</t>
+  </si>
+  <si>
+    <t>CUSP10</t>
+  </si>
+  <si>
+    <t>Mật khẩu mới yếu</t>
+  </si>
+  <si>
+    <t>newPassword="123"</t>
+  </si>
+  <si>
+    <t>CUSP11</t>
+  </si>
+  <si>
+    <t>oldPassword=null</t>
+  </si>
+  <si>
+    <t>CUSP12</t>
+  </si>
+  <si>
+    <t>CUSP13</t>
+  </si>
+  <si>
+    <t>Lấy danh sách booking</t>
+  </si>
+  <si>
+    <t>1. GET /profile/bookings</t>
+  </si>
+  <si>
+    <t>CUSP14</t>
+  </si>
+  <si>
+    <t>Không có booking</t>
+  </si>
+  <si>
+    <t>CUSP15</t>
+  </si>
+  <si>
+    <t>CUSP16</t>
+  </si>
+  <si>
+    <t>Lấy thống kê booking</t>
+  </si>
+  <si>
+    <t>1. GET /profile/bookings/summary</t>
+  </si>
+  <si>
+    <t>Trả về tổng số booking, trạng thái</t>
+  </si>
+  <si>
+    <t>CUSP17</t>
+  </si>
+  <si>
+    <t>CUSP18</t>
+  </si>
+  <si>
+    <t>Update profile quá dài</t>
+  </si>
+  <si>
+    <t>name dài 300 ký tự</t>
+  </si>
+  <si>
+    <t>CUSP19</t>
+  </si>
+  <si>
+    <t>Đổi password trùng mật khẩu cũ</t>
+  </si>
+  <si>
+    <t>old=new</t>
+  </si>
+  <si>
+    <t>CUSP20</t>
+  </si>
+  <si>
+    <t>Lấy booking với token hết hạn</t>
+  </si>
+  <si>
+    <t>Gọi API</t>
+  </si>
+  <si>
+    <t>Auto refresh token + thành công</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -658,6 +910,14 @@
       <sz val="11"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="163"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -667,7 +927,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -675,14 +935,32 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -986,7 +1264,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1026,214 +1304,284 @@
       <c r="J1" s="1"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="D3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" t="s">
+      <c r="B4" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" t="s">
-        <v>199</v>
-      </c>
-      <c r="C3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" t="s">
-        <v>199</v>
-      </c>
-      <c r="C4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" t="s">
-        <v>199</v>
-      </c>
-      <c r="C5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B6" t="s">
-        <v>199</v>
-      </c>
-      <c r="C6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E6" t="s">
-        <v>33</v>
-      </c>
-      <c r="F6" t="s">
-        <v>34</v>
-      </c>
-      <c r="G6" t="s">
-        <v>35</v>
+      <c r="D9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A10" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A11" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A12" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A13" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:J3"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="4" width="28" customWidth="1"/>
-    <col min="5" max="5" width="60" customWidth="1"/>
-    <col min="6" max="6" width="28" customWidth="1"/>
-    <col min="7" max="7" width="36" customWidth="1"/>
-    <col min="8" max="9" width="12" customWidth="1"/>
-    <col min="10" max="10" width="14" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10" ht="15" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>189</v>
-      </c>
-      <c r="B2" t="s">
-        <v>190</v>
-      </c>
-      <c r="C2" t="s">
-        <v>191</v>
-      </c>
-      <c r="D2" t="s">
-        <v>192</v>
-      </c>
-      <c r="E2" t="s">
-        <v>193</v>
-      </c>
-      <c r="F2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G2" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>195</v>
-      </c>
-      <c r="B3" t="s">
-        <v>190</v>
-      </c>
-      <c r="C3" t="s">
-        <v>196</v>
-      </c>
-      <c r="D3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" t="s">
-        <v>197</v>
-      </c>
-      <c r="F3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1280,140 +1628,140 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="F2" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="G2" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="B3" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="E3" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="F3" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="G3" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="B4" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="E4" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="F4" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="G4" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F5" t="s">
         <v>38</v>
       </c>
-      <c r="C5" t="s">
-        <v>54</v>
-      </c>
-      <c r="D5" t="s">
-        <v>55</v>
-      </c>
-      <c r="E5" t="s">
-        <v>56</v>
-      </c>
-      <c r="F5" t="s">
-        <v>57</v>
-      </c>
       <c r="G5" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F6" t="s">
         <v>38</v>
       </c>
-      <c r="C6" t="s">
-        <v>60</v>
-      </c>
-      <c r="D6" t="s">
-        <v>55</v>
-      </c>
-      <c r="E6" t="s">
-        <v>61</v>
-      </c>
-      <c r="F6" t="s">
-        <v>57</v>
-      </c>
       <c r="G6" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="B7" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="D7" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E7" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="F7" t="s">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="G7" t="s">
-        <v>67</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -1464,140 +1812,140 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="D2" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="E2" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="F2" t="s">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="G2" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="B3" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="C3" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="D3" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="E3" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="F3" t="s">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="G3" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="B4" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="C4" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="D4" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E4" t="s">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="F4" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="G4" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="B5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F5" t="s">
         <v>69</v>
       </c>
-      <c r="C5" t="s">
-        <v>86</v>
-      </c>
-      <c r="D5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5" t="s">
-        <v>87</v>
-      </c>
-      <c r="F5" t="s">
-        <v>88</v>
-      </c>
       <c r="G5" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="C6" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="D6" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="E6" t="s">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="F6" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="G6" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="B7" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="C7" t="s">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="D7" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E7" t="s">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="F7" t="s">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="G7" t="s">
-        <v>67</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -1648,94 +1996,94 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="B2" t="s">
-        <v>98</v>
+        <v>79</v>
       </c>
       <c r="C2" t="s">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="D2" t="s">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="E2" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="F2" t="s">
-        <v>102</v>
+        <v>83</v>
       </c>
       <c r="G2" t="s">
-        <v>103</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="B3" t="s">
-        <v>98</v>
+        <v>79</v>
       </c>
       <c r="C3" t="s">
-        <v>105</v>
+        <v>86</v>
       </c>
       <c r="D3" t="s">
-        <v>106</v>
+        <v>87</v>
       </c>
       <c r="E3" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="F3" t="s">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="G3" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="B4" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="C4" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="D4" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="E4" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="F4" t="s">
-        <v>102</v>
+        <v>83</v>
       </c>
       <c r="G4" t="s">
-        <v>103</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>113</v>
+        <v>94</v>
       </c>
       <c r="B5" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="C5" t="s">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="D5" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E5" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="F5" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="G5" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -1786,94 +2134,94 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="B2" t="s">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="C2" t="s">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="D2" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="E2" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="F2" t="s">
-        <v>120</v>
+        <v>101</v>
       </c>
       <c r="G2" t="s">
-        <v>103</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="B3" t="s">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="C3" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E3" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="F3" t="s">
-        <v>124</v>
+        <v>105</v>
       </c>
       <c r="G3" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="B4" t="s">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="C4" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="D4" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E4" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="F4" t="s">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="G4" t="s">
-        <v>127</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="B5" t="s">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="C5" t="s">
-        <v>129</v>
+        <v>110</v>
       </c>
       <c r="D5" t="s">
-        <v>130</v>
+        <v>111</v>
       </c>
       <c r="E5" t="s">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="F5" t="s">
-        <v>132</v>
+        <v>113</v>
       </c>
       <c r="G5" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -1883,7 +2231,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1924,94 +2272,462 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>133</v>
+        <v>230</v>
       </c>
       <c r="B2" t="s">
-        <v>134</v>
+        <v>231</v>
       </c>
       <c r="C2" t="s">
-        <v>135</v>
+        <v>232</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>137</v>
       </c>
       <c r="E2" t="s">
-        <v>136</v>
+        <v>233</v>
       </c>
       <c r="F2" t="s">
-        <v>137</v>
+        <v>13</v>
       </c>
       <c r="G2" t="s">
-        <v>103</v>
+        <v>234</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>138</v>
+        <v>235</v>
       </c>
       <c r="B3" t="s">
-        <v>134</v>
+        <v>231</v>
       </c>
       <c r="C3" t="s">
-        <v>139</v>
+        <v>236</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E3" t="s">
-        <v>140</v>
+        <v>233</v>
       </c>
       <c r="F3" t="s">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="G3" t="s">
-        <v>89</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>141</v>
+        <v>237</v>
       </c>
       <c r="B4" t="s">
-        <v>134</v>
+        <v>231</v>
       </c>
       <c r="C4" t="s">
-        <v>142</v>
+        <v>238</v>
       </c>
       <c r="D4" t="s">
-        <v>26</v>
+        <v>137</v>
       </c>
       <c r="E4" t="s">
-        <v>143</v>
+        <v>239</v>
       </c>
       <c r="F4" t="s">
-        <v>144</v>
+        <v>240</v>
       </c>
       <c r="G4" t="s">
-        <v>89</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>145</v>
+        <v>241</v>
       </c>
       <c r="B5" t="s">
-        <v>134</v>
+        <v>231</v>
       </c>
       <c r="C5" t="s">
-        <v>146</v>
+        <v>242</v>
       </c>
       <c r="D5" t="s">
-        <v>26</v>
+        <v>137</v>
       </c>
       <c r="E5" t="s">
-        <v>147</v>
+        <v>239</v>
       </c>
       <c r="F5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G5" t="s">
-        <v>148</v>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>243</v>
+      </c>
+      <c r="B6" t="s">
+        <v>231</v>
+      </c>
+      <c r="C6" t="s">
+        <v>244</v>
+      </c>
+      <c r="D6" t="s">
+        <v>137</v>
+      </c>
+      <c r="E6" t="s">
+        <v>239</v>
+      </c>
+      <c r="F6" t="s">
+        <v>245</v>
+      </c>
+      <c r="G6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>246</v>
+      </c>
+      <c r="B7" t="s">
+        <v>231</v>
+      </c>
+      <c r="C7" t="s">
+        <v>247</v>
+      </c>
+      <c r="D7" t="s">
+        <v>137</v>
+      </c>
+      <c r="E7" t="s">
+        <v>239</v>
+      </c>
+      <c r="F7" t="s">
+        <v>248</v>
+      </c>
+      <c r="G7" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>250</v>
+      </c>
+      <c r="B8" t="s">
+        <v>231</v>
+      </c>
+      <c r="C8" t="s">
+        <v>236</v>
+      </c>
+      <c r="D8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" t="s">
+        <v>239</v>
+      </c>
+      <c r="F8" t="s">
+        <v>251</v>
+      </c>
+      <c r="G8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>252</v>
+      </c>
+      <c r="B9" t="s">
+        <v>231</v>
+      </c>
+      <c r="C9" t="s">
+        <v>253</v>
+      </c>
+      <c r="D9" t="s">
+        <v>137</v>
+      </c>
+      <c r="E9" t="s">
+        <v>254</v>
+      </c>
+      <c r="F9" t="s">
+        <v>255</v>
+      </c>
+      <c r="G9" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>256</v>
+      </c>
+      <c r="B10" t="s">
+        <v>231</v>
+      </c>
+      <c r="C10" t="s">
+        <v>257</v>
+      </c>
+      <c r="D10" t="s">
+        <v>137</v>
+      </c>
+      <c r="E10" t="s">
+        <v>254</v>
+      </c>
+      <c r="F10" t="s">
+        <v>258</v>
+      </c>
+      <c r="G10" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>259</v>
+      </c>
+      <c r="B11" t="s">
+        <v>231</v>
+      </c>
+      <c r="C11" t="s">
+        <v>260</v>
+      </c>
+      <c r="D11" t="s">
+        <v>137</v>
+      </c>
+      <c r="E11" t="s">
+        <v>254</v>
+      </c>
+      <c r="F11" t="s">
+        <v>261</v>
+      </c>
+      <c r="G11" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>262</v>
+      </c>
+      <c r="B12" t="s">
+        <v>231</v>
+      </c>
+      <c r="C12" t="s">
+        <v>217</v>
+      </c>
+      <c r="D12" t="s">
+        <v>137</v>
+      </c>
+      <c r="E12" t="s">
+        <v>254</v>
+      </c>
+      <c r="F12" t="s">
+        <v>263</v>
+      </c>
+      <c r="G12" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>264</v>
+      </c>
+      <c r="B13" t="s">
+        <v>231</v>
+      </c>
+      <c r="C13" t="s">
+        <v>236</v>
+      </c>
+      <c r="D13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" t="s">
+        <v>254</v>
+      </c>
+      <c r="F13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>265</v>
+      </c>
+      <c r="B14" t="s">
+        <v>231</v>
+      </c>
+      <c r="C14" t="s">
+        <v>266</v>
+      </c>
+      <c r="D14" t="s">
+        <v>137</v>
+      </c>
+      <c r="E14" t="s">
+        <v>267</v>
+      </c>
+      <c r="F14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>268</v>
+      </c>
+      <c r="B15" t="s">
+        <v>231</v>
+      </c>
+      <c r="C15" t="s">
+        <v>269</v>
+      </c>
+      <c r="D15" t="s">
+        <v>137</v>
+      </c>
+      <c r="E15" t="s">
+        <v>267</v>
+      </c>
+      <c r="F15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>270</v>
+      </c>
+      <c r="B16" t="s">
+        <v>231</v>
+      </c>
+      <c r="C16" t="s">
+        <v>236</v>
+      </c>
+      <c r="D16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" t="s">
+        <v>267</v>
+      </c>
+      <c r="F16" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>271</v>
+      </c>
+      <c r="B17" t="s">
+        <v>231</v>
+      </c>
+      <c r="C17" t="s">
+        <v>272</v>
+      </c>
+      <c r="D17" t="s">
+        <v>137</v>
+      </c>
+      <c r="E17" t="s">
+        <v>273</v>
+      </c>
+      <c r="F17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G17" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>275</v>
+      </c>
+      <c r="B18" t="s">
+        <v>231</v>
+      </c>
+      <c r="C18" t="s">
+        <v>236</v>
+      </c>
+      <c r="D18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" t="s">
+        <v>273</v>
+      </c>
+      <c r="F18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>276</v>
+      </c>
+      <c r="B19" t="s">
+        <v>231</v>
+      </c>
+      <c r="C19" t="s">
+        <v>277</v>
+      </c>
+      <c r="D19" t="s">
+        <v>137</v>
+      </c>
+      <c r="E19" t="s">
+        <v>239</v>
+      </c>
+      <c r="F19" t="s">
+        <v>278</v>
+      </c>
+      <c r="G19" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>279</v>
+      </c>
+      <c r="B20" t="s">
+        <v>231</v>
+      </c>
+      <c r="C20" t="s">
+        <v>280</v>
+      </c>
+      <c r="D20" t="s">
+        <v>137</v>
+      </c>
+      <c r="E20" t="s">
+        <v>254</v>
+      </c>
+      <c r="F20" t="s">
+        <v>281</v>
+      </c>
+      <c r="G20" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>282</v>
+      </c>
+      <c r="B21" t="s">
+        <v>231</v>
+      </c>
+      <c r="C21" t="s">
+        <v>283</v>
+      </c>
+      <c r="D21" t="s">
+        <v>114</v>
+      </c>
+      <c r="E21" t="s">
+        <v>267</v>
+      </c>
+      <c r="F21" t="s">
+        <v>284</v>
+      </c>
+      <c r="G21" t="s">
+        <v>285</v>
       </c>
     </row>
   </sheetData>
@@ -2020,21 +2736,19 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:J5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1ED523F6-31FB-4005-93D2-E64F5F663B90}">
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="4" width="28" customWidth="1"/>
-    <col min="5" max="5" width="60" customWidth="1"/>
-    <col min="6" max="6" width="28" customWidth="1"/>
-    <col min="7" max="7" width="36" customWidth="1"/>
-    <col min="8" max="9" width="12" customWidth="1"/>
-    <col min="10" max="10" width="14" customWidth="1"/>
+    <col min="2" max="2" width="9.125" customWidth="1"/>
+    <col min="3" max="3" width="22.125" customWidth="1"/>
+    <col min="4" max="4" width="18.25" customWidth="1"/>
+    <col min="5" max="5" width="26.375" customWidth="1"/>
+    <col min="6" max="6" width="44" customWidth="1"/>
+    <col min="7" max="7" width="22.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" ht="30" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2056,200 +2770,428 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E2" t="s">
+        <v>144</v>
+      </c>
+      <c r="F2" t="s">
+        <v>145</v>
+      </c>
+      <c r="G2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>146</v>
+      </c>
+      <c r="B3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E3" t="s">
+        <v>144</v>
+      </c>
+      <c r="F3" t="s">
+        <v>148</v>
+      </c>
+      <c r="G3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
         <v>149</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C4" t="s">
         <v>150</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D4" t="s">
+        <v>137</v>
+      </c>
+      <c r="E4" t="s">
+        <v>144</v>
+      </c>
+      <c r="F4" t="s">
         <v>151</v>
       </c>
-      <c r="D2" t="s">
+      <c r="G4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
         <v>152</v>
       </c>
-      <c r="E2" t="s">
+      <c r="B5" t="s">
+        <v>135</v>
+      </c>
+      <c r="C5" t="s">
         <v>153</v>
       </c>
-      <c r="F2" t="s">
+      <c r="D5" t="s">
+        <v>137</v>
+      </c>
+      <c r="E5" t="s">
+        <v>144</v>
+      </c>
+      <c r="F5" t="s">
         <v>154</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+      <c r="B6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C6" t="s">
         <v>156</v>
       </c>
-      <c r="B3" t="s">
-        <v>150</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="D6" t="s">
+        <v>137</v>
+      </c>
+      <c r="E6" t="s">
+        <v>144</v>
+      </c>
+      <c r="F6" t="s">
         <v>157</v>
       </c>
-      <c r="D3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="G6" t="s">
         <v>158</v>
       </c>
-      <c r="F3" t="s">
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>134</v>
+      </c>
+      <c r="B7" t="s">
+        <v>135</v>
+      </c>
+      <c r="C7" t="s">
+        <v>136</v>
+      </c>
+      <c r="D7" t="s">
+        <v>137</v>
+      </c>
+      <c r="E7" t="s">
+        <v>138</v>
+      </c>
+      <c r="F7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>140</v>
+      </c>
+      <c r="B8" t="s">
+        <v>135</v>
+      </c>
+      <c r="C8" t="s">
+        <v>141</v>
+      </c>
+      <c r="D8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" t="s">
+        <v>138</v>
+      </c>
+      <c r="F8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
         <v>159</v>
       </c>
-      <c r="G3" t="s">
+      <c r="B9" t="s">
+        <v>135</v>
+      </c>
+      <c r="C9" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+      <c r="D9" t="s">
+        <v>137</v>
+      </c>
+      <c r="E9" t="s">
+        <v>161</v>
+      </c>
+      <c r="F9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" t="s">
         <v>162</v>
       </c>
-      <c r="B4" t="s">
-        <v>150</v>
-      </c>
-      <c r="C4" t="s">
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
         <v>163</v>
       </c>
-      <c r="D4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="B10" t="s">
+        <v>135</v>
+      </c>
+      <c r="C10" t="s">
         <v>164</v>
       </c>
-      <c r="F4" t="s">
+      <c r="D10" t="s">
+        <v>137</v>
+      </c>
+      <c r="E10" t="s">
+        <v>161</v>
+      </c>
+      <c r="F10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" t="s">
         <v>165</v>
       </c>
-      <c r="G4" t="s">
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
+      <c r="B11" t="s">
+        <v>135</v>
+      </c>
+      <c r="C11" t="s">
+        <v>141</v>
+      </c>
+      <c r="D11" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" t="s">
+        <v>161</v>
+      </c>
+      <c r="F11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
         <v>167</v>
       </c>
-      <c r="B5" t="s">
-        <v>150</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="B12" t="s">
+        <v>135</v>
+      </c>
+      <c r="C12" t="s">
         <v>168</v>
       </c>
-      <c r="D5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="D12" t="s">
         <v>169</v>
       </c>
-      <c r="F5" t="s">
+      <c r="E12" t="s">
         <v>170</v>
       </c>
-      <c r="G5" t="s">
+      <c r="F12" t="s">
         <v>171</v>
       </c>
+      <c r="G12" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>172</v>
+      </c>
+      <c r="B13" t="s">
+        <v>135</v>
+      </c>
+      <c r="C13" t="s">
+        <v>173</v>
+      </c>
+      <c r="D13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" t="s">
+        <v>170</v>
+      </c>
+      <c r="F13" t="s">
+        <v>174</v>
+      </c>
+      <c r="G13" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>176</v>
+      </c>
+      <c r="B14" t="s">
+        <v>135</v>
+      </c>
+      <c r="C14" t="s">
+        <v>177</v>
+      </c>
+      <c r="D14" t="s">
+        <v>178</v>
+      </c>
+      <c r="E14" t="s">
+        <v>179</v>
+      </c>
+      <c r="F14" t="s">
+        <v>171</v>
+      </c>
+      <c r="G14" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>181</v>
+      </c>
+      <c r="B15" t="s">
+        <v>135</v>
+      </c>
+      <c r="C15" t="s">
+        <v>182</v>
+      </c>
+      <c r="D15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" t="s">
+        <v>179</v>
+      </c>
+      <c r="F15" t="s">
+        <v>183</v>
+      </c>
+      <c r="G15" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>185</v>
+      </c>
+      <c r="B16" t="s">
+        <v>135</v>
+      </c>
+      <c r="C16" t="s">
+        <v>186</v>
+      </c>
+      <c r="D16" t="s">
+        <v>187</v>
+      </c>
+      <c r="E16" t="s">
+        <v>188</v>
+      </c>
+      <c r="F16" t="s">
+        <v>38</v>
+      </c>
+      <c r="G16" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>189</v>
+      </c>
+      <c r="B17" t="s">
+        <v>135</v>
+      </c>
+      <c r="C17" t="s">
+        <v>190</v>
+      </c>
+      <c r="D17" t="s">
+        <v>137</v>
+      </c>
+      <c r="E17" t="s">
+        <v>188</v>
+      </c>
+      <c r="F17" t="s">
+        <v>191</v>
+      </c>
+      <c r="G17" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>193</v>
+      </c>
+      <c r="B18" t="s">
+        <v>135</v>
+      </c>
+      <c r="C18" t="s">
+        <v>194</v>
+      </c>
+      <c r="D18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" t="s">
+        <v>188</v>
+      </c>
+      <c r="F18" t="s">
+        <v>47</v>
+      </c>
+      <c r="G18" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>195</v>
+      </c>
+      <c r="B19" t="s">
+        <v>135</v>
+      </c>
+      <c r="C19" t="s">
+        <v>141</v>
+      </c>
+      <c r="D19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" t="s">
+        <v>188</v>
+      </c>
+      <c r="F19" t="s">
+        <v>38</v>
+      </c>
+      <c r="G19" t="s">
+        <v>16</v>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:J3"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="4" width="28" customWidth="1"/>
-    <col min="5" max="5" width="60" customWidth="1"/>
-    <col min="6" max="6" width="28" customWidth="1"/>
-    <col min="7" max="7" width="36" customWidth="1"/>
-    <col min="8" max="9" width="12" customWidth="1"/>
-    <col min="10" max="10" width="14" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10" ht="15" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>172</v>
-      </c>
-      <c r="B2" t="s">
-        <v>161</v>
-      </c>
-      <c r="C2" t="s">
-        <v>173</v>
-      </c>
-      <c r="D2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E2" t="s">
-        <v>174</v>
-      </c>
-      <c r="F2" t="s">
-        <v>175</v>
-      </c>
-      <c r="G2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>177</v>
-      </c>
-      <c r="B3" t="s">
-        <v>161</v>
-      </c>
-      <c r="C3" t="s">
-        <v>178</v>
-      </c>
-      <c r="D3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" t="s">
-        <v>179</v>
-      </c>
-      <c r="F3" t="s">
-        <v>180</v>
-      </c>
-      <c r="G3" t="s">
-        <v>181</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -2292,48 +3234,140 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>182</v>
+        <v>116</v>
       </c>
       <c r="B2" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>183</v>
+        <v>117</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E2" t="s">
-        <v>184</v>
+        <v>118</v>
       </c>
       <c r="F2" t="s">
-        <v>185</v>
+        <v>119</v>
       </c>
       <c r="G2" t="s">
-        <v>171</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>186</v>
+        <v>120</v>
       </c>
       <c r="B3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>187</v>
+        <v>121</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E3" t="s">
-        <v>184</v>
+        <v>118</v>
       </c>
       <c r="F3" t="s">
-        <v>188</v>
+        <v>122</v>
       </c>
       <c r="G3" t="s">
-        <v>171</v>
+        <v>115</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+  <dimension ref="A1:J3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="4" width="28" customWidth="1"/>
+    <col min="5" max="5" width="60" customWidth="1"/>
+    <col min="6" max="6" width="28" customWidth="1"/>
+    <col min="7" max="7" width="36" customWidth="1"/>
+    <col min="8" max="9" width="12" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="15" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E2" t="s">
+        <v>127</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C3" t="s">
+        <v>130</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>131</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" t="s">
+        <v>132</v>
       </c>
     </row>
   </sheetData>

--- a/docs/HMS_TestCases.xlsx
+++ b/docs/HMS_TestCases.xlsx
@@ -8,20 +8,25 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\HOC_TAP\QL-KhachSan\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF039AA3-DEEE-425D-A8B9-05D5154DADDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C12ACE1-99D3-47AA-9E94-43BB47E2A288}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4680" yWindow="2250" windowWidth="21600" windowHeight="11835" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7080" yWindow="2790" windowWidth="21600" windowHeight="11835" firstSheet="6" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AUTH" sheetId="1" r:id="rId1"/>
     <sheet name="ROOM" sheetId="2" r:id="rId2"/>
-    <sheet name="BOOKING" sheetId="3" r:id="rId3"/>
-    <sheet name="CHECKIN" sheetId="4" r:id="rId4"/>
-    <sheet name="PAYMENT" sheetId="5" r:id="rId5"/>
-    <sheet name="CUSTOMER" sheetId="6" r:id="rId6"/>
-    <sheet name="REVIEW" sheetId="11" r:id="rId7"/>
-    <sheet name="SECURITY" sheetId="9" r:id="rId8"/>
-    <sheet name="REGRESSION" sheetId="10" r:id="rId9"/>
+    <sheet name="STAFF" sheetId="12" r:id="rId3"/>
+    <sheet name="HOTEL" sheetId="13" r:id="rId4"/>
+    <sheet name="BOOKING" sheetId="3" r:id="rId5"/>
+    <sheet name="SERVICES" sheetId="14" r:id="rId6"/>
+    <sheet name="CHECKIN" sheetId="4" r:id="rId7"/>
+    <sheet name="PAYMENT" sheetId="5" r:id="rId8"/>
+    <sheet name="REVIEW" sheetId="11" r:id="rId9"/>
+    <sheet name="CUSTOMER" sheetId="6" r:id="rId10"/>
+    <sheet name="PROFILE" sheetId="16" r:id="rId11"/>
+    <sheet name="EDGE" sheetId="17" r:id="rId12"/>
+    <sheet name="SECURITY" sheetId="9" r:id="rId13"/>
+    <sheet name="REGRESSION" sheetId="10" r:id="rId14"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -33,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1439" uniqueCount="849">
   <si>
     <t>TC_ID</t>
   </si>
@@ -92,18 +97,12 @@
     <t>ROOM01</t>
   </si>
   <si>
-    <t>Room</t>
-  </si>
-  <si>
     <t>Thêm phòng hợp lệ</t>
   </si>
   <si>
     <t>Admin login</t>
   </si>
   <si>
-    <t>1. Gửi POST /rooms</t>
-  </si>
-  <si>
     <t>name=101, price=500000</t>
   </si>
   <si>
@@ -116,9 +115,6 @@
     <t>Thiếu tên phòng</t>
   </si>
   <si>
-    <t>1. POST /rooms thiếu name</t>
-  </si>
-  <si>
     <t>name=null</t>
   </si>
   <si>
@@ -131,9 +127,6 @@
     <t>Giá âm</t>
   </si>
   <si>
-    <t>1. POST /rooms</t>
-  </si>
-  <si>
     <t>price=-1</t>
   </si>
   <si>
@@ -146,9 +139,6 @@
     <t>Phòng tồn tại</t>
   </si>
   <si>
-    <t>1. PUT /rooms/:id</t>
-  </si>
-  <si>
     <t>id=1</t>
   </si>
   <si>
@@ -161,9 +151,6 @@
     <t>Xóa phòng</t>
   </si>
   <si>
-    <t>1. DELETE /rooms/:id</t>
-  </si>
-  <si>
     <t>Xóa thành công</t>
   </si>
   <si>
@@ -173,9 +160,6 @@
     <t>Xóa phòng không tồn tại</t>
   </si>
   <si>
-    <t>1. DELETE /rooms/999</t>
-  </si>
-  <si>
     <t>id=999</t>
   </si>
   <si>
@@ -194,9 +178,6 @@
     <t>Phòng trống</t>
   </si>
   <si>
-    <t>1. POST /bookings</t>
-  </si>
-  <si>
     <t>room=1, date valid</t>
   </si>
   <si>
@@ -212,9 +193,6 @@
     <t>Phòng bận</t>
   </si>
   <si>
-    <t>1. POST booking trùng</t>
-  </si>
-  <si>
     <t>room busy</t>
   </si>
   <si>
@@ -251,189 +229,78 @@
     <t>BOOK05</t>
   </si>
   <si>
-    <t>Hủy booking</t>
-  </si>
-  <si>
     <t>Booking tồn tại</t>
   </si>
   <si>
-    <t>1. DELETE booking</t>
-  </si>
-  <si>
-    <t>Hủy thành công</t>
-  </si>
-  <si>
     <t>BOOK06</t>
   </si>
   <si>
-    <t>Hủy sai id</t>
-  </si>
-  <si>
     <t>CI01</t>
   </si>
   <si>
-    <t>Checkin</t>
-  </si>
-  <si>
     <t>Check-in hợp lệ</t>
   </si>
   <si>
     <t>Booking hợp lệ</t>
   </si>
   <si>
-    <t>1. POST /checkin</t>
-  </si>
-  <si>
-    <t>booking_id=1</t>
-  </si>
-  <si>
     <t>Thành công</t>
   </si>
   <si>
     <t>CI02</t>
   </si>
   <si>
-    <t>Check-in sớm</t>
-  </si>
-  <si>
-    <t>Chưa tới ngày</t>
-  </si>
-  <si>
-    <t>date early</t>
-  </si>
-  <si>
     <t>CI03</t>
   </si>
   <si>
-    <t>Checkout</t>
-  </si>
-  <si>
     <t>Check-out hợp lệ</t>
   </si>
   <si>
-    <t>Đã check-in</t>
-  </si>
-  <si>
-    <t>1. POST /checkout</t>
-  </si>
-  <si>
     <t>CI04</t>
   </si>
   <si>
-    <t>Check-out chưa check-in</t>
-  </si>
-  <si>
-    <t>booking_id=2</t>
-  </si>
-  <si>
     <t>PAY01</t>
   </si>
   <si>
     <t>Payment</t>
   </si>
   <si>
-    <t>Thanh toán hợp lệ</t>
-  </si>
-  <si>
-    <t>1. POST /payments</t>
-  </si>
-  <si>
-    <t>amount=1000000</t>
-  </si>
-  <si>
     <t>PAY02</t>
   </si>
   <si>
-    <t>Số tiền âm</t>
-  </si>
-  <si>
-    <t>1. POST payment</t>
-  </si>
-  <si>
-    <t>amount=-1</t>
-  </si>
-  <si>
     <t>PAY03</t>
   </si>
   <si>
-    <t>Sai booking</t>
-  </si>
-  <si>
-    <t>404</t>
-  </si>
-  <si>
     <t>PAY04</t>
   </si>
   <si>
-    <t>Thanh toán 2 lần</t>
-  </si>
-  <si>
-    <t>Đã thanh toán</t>
-  </si>
-  <si>
-    <t>1. POST lại</t>
-  </si>
-  <si>
-    <t>duplicate</t>
-  </si>
-  <si>
     <t>Token hết hạn</t>
   </si>
   <si>
-    <t>401</t>
-  </si>
-  <si>
     <t>SEC01</t>
   </si>
   <si>
-    <t>Không token</t>
-  </si>
-  <si>
     <t>1. Gọi API</t>
   </si>
   <si>
-    <t>no token</t>
-  </si>
-  <si>
     <t>SEC02</t>
   </si>
   <si>
     <t>Token giả</t>
   </si>
   <si>
-    <t>fake token</t>
-  </si>
-  <si>
     <t>REG01</t>
   </si>
   <si>
     <t>Regression</t>
   </si>
   <si>
-    <t>Fix booking</t>
-  </si>
-  <si>
-    <t>Bug đã fix</t>
-  </si>
-  <si>
-    <t>1. Test lại flow</t>
-  </si>
-  <si>
     <t>Không lỗi</t>
   </si>
   <si>
     <t>REG02</t>
   </si>
   <si>
-    <t>Update room</t>
-  </si>
-  <si>
-    <t>1. Update room</t>
-  </si>
-  <si>
-    <t>Không ảnh hưởng booking</t>
-  </si>
-  <si>
     <t>Auth</t>
   </si>
   <si>
@@ -891,13 +758,1856 @@
   </si>
   <si>
     <t>Auto refresh token + thành công</t>
+  </si>
+  <si>
+    <t>AUTH13</t>
+  </si>
+  <si>
+    <t>Gắn Authorization header</t>
+  </si>
+  <si>
+    <t>Có accessToken</t>
+  </si>
+  <si>
+    <t>1. Gửi request API</t>
+  </si>
+  <si>
+    <t>accessToken=abc</t>
+  </si>
+  <si>
+    <t>Header có Bearer token</t>
+  </si>
+  <si>
+    <t>AUTH14</t>
+  </si>
+  <si>
+    <t>Không có token</t>
+  </si>
+  <si>
+    <t>Không có Authorization header</t>
+  </si>
+  <si>
+    <t>Admin-Room</t>
+  </si>
+  <si>
+    <t>1. Gửi POST/admin /rooms</t>
+  </si>
+  <si>
+    <t>1. POST /admin/rooms thiếu name</t>
+  </si>
+  <si>
+    <t>1. POST /admin/rooms</t>
+  </si>
+  <si>
+    <t>1. PUT /admin/rooms/:id</t>
+  </si>
+  <si>
+    <t>1. DELETE /admin/rooms/:id</t>
+  </si>
+  <si>
+    <t>1. DELETE /admin/rooms/999</t>
+  </si>
+  <si>
+    <t>ROOM07</t>
+  </si>
+  <si>
+    <t>Tìm phòng theo số phòng</t>
+  </si>
+  <si>
+    <t>Nhập searchterm</t>
+  </si>
+  <si>
+    <t>searchterm=P101</t>
+  </si>
+  <si>
+    <t>Chỉ hiện phòng P101</t>
+  </si>
+  <si>
+    <t>ROOM08</t>
+  </si>
+  <si>
+    <t>Reception-Room</t>
+  </si>
+  <si>
+    <t>Tạo phòng hợp lệ</t>
+  </si>
+  <si>
+    <t>Hotel &amp; RoomType tồn tại</t>
+  </si>
+  <si>
+    <t>POST /api/reception/rooms</t>
+  </si>
+  <si>
+    <t>hotelId=1, roomTypeId=2, roomNumber=101</t>
+  </si>
+  <si>
+    <t>201 OK; status=AVAILABLE</t>
+  </si>
+  <si>
+    <t>ROOM09</t>
+  </si>
+  <si>
+    <t>Tạo phòng — trùng số phòng</t>
+  </si>
+  <si>
+    <t>Đã có phòng 101 trong hotel 1</t>
+  </si>
+  <si>
+    <t>hotelId=1, roomNumber=101</t>
+  </si>
+  <si>
+    <t>400 — Room number already exists</t>
+  </si>
+  <si>
+    <t>ROOM10</t>
+  </si>
+  <si>
+    <t>Tạo phòng — thiếu field bắt buộc</t>
+  </si>
+  <si>
+    <t>POST /api/reception/rooms với body {}</t>
+  </si>
+  <si>
+    <t>body={}</t>
+  </si>
+  <si>
+    <t>400 — Validation failed (hotelId/roomTypeId/roomNumber)</t>
+  </si>
+  <si>
+    <t>ROOM11</t>
+  </si>
+  <si>
+    <t>Lấy danh sách phòng (có/không filter)</t>
+  </si>
+  <si>
+    <t>Có phòng trong DB</t>
+  </si>
+  <si>
+    <t>GET /api/reception/rooms?hotelId=&amp;status=</t>
+  </si>
+  <si>
+    <t>filter status=AVAILABLE</t>
+  </si>
+  <si>
+    <t>200 OK; list phòng theo filter</t>
+  </si>
+  <si>
+    <t>ROOM12</t>
+  </si>
+  <si>
+    <t>Xem chi tiết phòng</t>
+  </si>
+  <si>
+    <t>Phòng id=10 tồn tại</t>
+  </si>
+  <si>
+    <t>GET /api/reception/rooms/{id}</t>
+  </si>
+  <si>
+    <t>id=10 / id=99</t>
+  </si>
+  <si>
+    <t>200 OK khi tồn tại; 404 khi không tồn tại</t>
+  </si>
+  <si>
+    <t>ROOM13</t>
+  </si>
+  <si>
+    <t>State transition — chuyển hợp lệ</t>
+  </si>
+  <si>
+    <t>Phòng có status hiện tại</t>
+  </si>
+  <si>
+    <t>PATCH /api/reception/rooms/{id}/status</t>
+  </si>
+  <si>
+    <t>AVAILABLE→OCCUPIED; OCCUPIED→CLEANING; MAINTENANCE→AVAILABLE</t>
+  </si>
+  <si>
+    <t>200 OK; status được cập nhật</t>
+  </si>
+  <si>
+    <t>ROOM14</t>
+  </si>
+  <si>
+    <t>State transition — chuyển không hợp lệ</t>
+  </si>
+  <si>
+    <t>OCCUPIED→AVAILABLE; RESERVED→CLEANING; MAINTENANCE→OCCUPIED</t>
+  </si>
+  <si>
+    <t>400 — Invalid room status transition</t>
+  </si>
+  <si>
+    <t>ROOM15</t>
+  </si>
+  <si>
+    <t>State transition — cùng status (no-op)</t>
+  </si>
+  <si>
+    <t>Phòng status=AVAILABLE</t>
+  </si>
+  <si>
+    <t>status=AVAILABLE</t>
+  </si>
+  <si>
+    <t>200 OK; trả về phòng hiện tại; không ghi DB</t>
+  </si>
+  <si>
+    <t>ROOM16</t>
+  </si>
+  <si>
+    <t>DELETE /api/reception/rooms/{id}</t>
+  </si>
+  <si>
+    <t>status=AVAILABLE / status=OCCUPIED / id=99</t>
+  </si>
+  <si>
+    <t>204 khi không OCCUPIED; 400 khi OCCUPIED; 404 khi không tồn tại</t>
+  </si>
+  <si>
+    <t>ROOM17</t>
+  </si>
+  <si>
+    <t>Tra cứu khách sạn &amp; loại phòng</t>
+  </si>
+  <si>
+    <t>Có hotel &amp; roomType</t>
+  </si>
+  <si>
+    <t>GET /api/reception/hotels
+GET /api/reception/room-types?hotelId=1</t>
+  </si>
+  <si>
+    <t>200 OK; trả về list options cho dropdown</t>
+  </si>
+  <si>
+    <t>ROOM18</t>
+  </si>
+  <si>
+    <t>Authorization</t>
+  </si>
+  <si>
+    <t>User role khác RECEPTION</t>
+  </si>
+  <si>
+    <t>GET /api/reception/rooms</t>
+  </si>
+  <si>
+    <t>role=CUSTOMER / no token</t>
+  </si>
+  <si>
+    <t>403 với CUSTOMER; 401 khi không có token</t>
+  </si>
+  <si>
+    <t>ROOM19</t>
+  </si>
+  <si>
+    <t>Admin-RoomType</t>
+  </si>
+  <si>
+    <t>Xem danh sách loại phòng</t>
+  </si>
+  <si>
+    <t>Loại phòng trong DB</t>
+  </si>
+  <si>
+    <t>GET /api/admin/room-types</t>
+  </si>
+  <si>
+    <t>Hiển thị danh sách loại phòng</t>
+  </si>
+  <si>
+    <t>ROOM20</t>
+  </si>
+  <si>
+    <t>Thêm loại phòng hợp lệ</t>
+  </si>
+  <si>
+    <t>POST /api/admin/room-types</t>
+  </si>
+  <si>
+    <t>name=VIP, capacity=3, basePrice=2000000, desc=Xe trung chuyển</t>
+  </si>
+  <si>
+    <t>Tạo loại phòng thành công
+Tên loại phòng=VIP; Sức chứa=3; Giá phòng(1 đêm)=200000, Mô tả=Xe trung chuyển</t>
+  </si>
+  <si>
+    <t>ROOM21</t>
+  </si>
+  <si>
+    <t>Thêm loại phòng - giá &lt; 0</t>
+  </si>
+  <si>
+    <t>basePrice=-200000</t>
+  </si>
+  <si>
+    <t>Giá phòng không hợp lệ!</t>
+  </si>
+  <si>
+    <t>ROOM22</t>
+  </si>
+  <si>
+    <t>Thêm loại phòng - giá = 0</t>
+  </si>
+  <si>
+    <t>basePrice= 0</t>
+  </si>
+  <si>
+    <t>ROOM23</t>
+  </si>
+  <si>
+    <t>Thêm loại phòng - sức chứa &lt; 0</t>
+  </si>
+  <si>
+    <t>capacity=-1</t>
+  </si>
+  <si>
+    <t>Sức chứa không hợp lệ!</t>
+  </si>
+  <si>
+    <t>ROOM24</t>
+  </si>
+  <si>
+    <t>Thêm loại phòng - sức chứa = 0</t>
+  </si>
+  <si>
+    <t>capacity=0</t>
+  </si>
+  <si>
+    <t>ROOM25</t>
+  </si>
+  <si>
+    <t>Thêm loại phòng - trùng tất cả trường trong form</t>
+  </si>
+  <si>
+    <t>Loại phòng: "Single", 1, 200000, "Wifi"</t>
+  </si>
+  <si>
+    <t>name=Single, capacity=1, basePrice=200000, desc=Wifi</t>
+  </si>
+  <si>
+    <t>Loại phòng này đã tồn tại!</t>
+  </si>
+  <si>
+    <t>ROOM26</t>
+  </si>
+  <si>
+    <t>Thêm loại phòng - không trùng tất cả trường trong form</t>
+  </si>
+  <si>
+    <t>name=Single, capacity=3, basePrice=200000, desc=Wifi</t>
+  </si>
+  <si>
+    <t>Thêm mới thành công!</t>
+  </si>
+  <si>
+    <t>ROOM27</t>
+  </si>
+  <si>
+    <t>Cập nhật hợp lệ</t>
+  </si>
+  <si>
+    <t>Loại phòng tồn tại</t>
+  </si>
+  <si>
+    <t>PUT /api/admin/room-types/:id</t>
+  </si>
+  <si>
+    <t>id=1, basePrice=500000</t>
+  </si>
+  <si>
+    <t>Cập nhật thành công!</t>
+  </si>
+  <si>
+    <t>ROOM28</t>
+  </si>
+  <si>
+    <t>Cập nhật - giá không hợp lệ</t>
+  </si>
+  <si>
+    <t>basePrice=-100</t>
+  </si>
+  <si>
+    <t>Giá phòng cập nhật không hợp lệ!</t>
+  </si>
+  <si>
+    <t>ROOM29</t>
+  </si>
+  <si>
+    <t>Cập nhật - sức chứa không hợp lệ</t>
+  </si>
+  <si>
+    <t>Sức chứa cập nhật không hợp lệ!</t>
+  </si>
+  <si>
+    <t>ROOM30</t>
+  </si>
+  <si>
+    <t>Cập nhật ID không tồn tại</t>
+  </si>
+  <si>
+    <t>PUT /api/admin/room-types/9999</t>
+  </si>
+  <si>
+    <t>id=9999</t>
+  </si>
+  <si>
+    <t>Không tìm thấy loại phòng!</t>
+  </si>
+  <si>
+    <t>ROOM31</t>
+  </si>
+  <si>
+    <t>Xóa — không có phòng sử dụng</t>
+  </si>
+  <si>
+    <t>Loại phòng chưa gán cho phòng</t>
+  </si>
+  <si>
+    <t>DELETE /api/admin/room-types/:id</t>
+  </si>
+  <si>
+    <t>id loại phòng trống</t>
+  </si>
+  <si>
+    <t>ROOM32</t>
+  </si>
+  <si>
+    <t>Xóa — đang có phòng sử dụng</t>
+  </si>
+  <si>
+    <t>Loại phòng gán cho phòng</t>
+  </si>
+  <si>
+    <t>id=4</t>
+  </si>
+  <si>
+    <t>Loại phòng có thể đang được sử dụng ở danh sách phòng! ID=4 không xóa</t>
+  </si>
+  <si>
+    <t>ROOM33</t>
+  </si>
+  <si>
+    <t>Tìm kiếm loại phòng đã có</t>
+  </si>
+  <si>
+    <t>Loại phòng tồn tại trong DB</t>
+  </si>
+  <si>
+    <t>nhập searchTerm</t>
+  </si>
+  <si>
+    <t>searchTerm=Single</t>
+  </si>
+  <si>
+    <t>Chỉ hiện loại phòng chứa "Single"</t>
+  </si>
+  <si>
+    <t>ROOM34</t>
+  </si>
+  <si>
+    <t>Tìm kiếm loại phòng không có</t>
+  </si>
+  <si>
+    <t>Loại phòng không tồn tại trong DB</t>
+  </si>
+  <si>
+    <t>searchTerm=aaaaa</t>
+  </si>
+  <si>
+    <t>Không tìm thấy loại phòng nào phù hợp...</t>
+  </si>
+  <si>
+    <t>STF01</t>
+  </si>
+  <si>
+    <t>Staff</t>
+  </si>
+  <si>
+    <t>Xem danh sách nhân viên</t>
+  </si>
+  <si>
+    <t>Nhân viên(Reception/admin) tồn tại trong DB</t>
+  </si>
+  <si>
+    <t>GET /api/admin/staff</t>
+  </si>
+  <si>
+    <t>Hiển thị danh sách NV (ADMIN, RECEPTION)</t>
+  </si>
+  <si>
+    <t>STF02</t>
+  </si>
+  <si>
+    <t>Thêm NV hợp lệ</t>
+  </si>
+  <si>
+    <t>Admin login, có KS trong DB</t>
+  </si>
+  <si>
+    <t>POST /api/admin/staff</t>
+  </si>
+  <si>
+    <t>fullName=Tran B, email=b@test.com, phone=0901234567, password=123456, hotelId=5</t>
+  </si>
+  <si>
+    <t>Tạo nhân viên thành công.</t>
+  </si>
+  <si>
+    <t>STF03</t>
+  </si>
+  <si>
+    <t>Thêm NV thiếu thông tin</t>
+  </si>
+  <si>
+    <t>fullName=null</t>
+  </si>
+  <si>
+    <t>Vui lòng nhập đầy đủ thông tin!</t>
+  </si>
+  <si>
+    <t>STF04</t>
+  </si>
+  <si>
+    <t>Thêm NV trùng email</t>
+  </si>
+  <si>
+    <t>Email đã tồn tại trong DB</t>
+  </si>
+  <si>
+    <t>email=a@test.com</t>
+  </si>
+  <si>
+    <t>Email này đã tồn tại!</t>
+  </si>
+  <si>
+    <t>STF05</t>
+  </si>
+  <si>
+    <t>Thêm NV trùng SĐT</t>
+  </si>
+  <si>
+    <t>SĐT đã tồn tại trong DB</t>
+  </si>
+  <si>
+    <t>phone=0901111111</t>
+  </si>
+  <si>
+    <t>Số điện thoại này đã tồn tại!</t>
+  </si>
+  <si>
+    <t>STF06</t>
+  </si>
+  <si>
+    <t>Thêm NV - không chọn role</t>
+  </si>
+  <si>
+    <t>role=null</t>
+  </si>
+  <si>
+    <t>Tạo thành công; role=RECEPTION</t>
+  </si>
+  <si>
+    <t>STF07</t>
+  </si>
+  <si>
+    <t>Thêm NV - NV chưa gán KS</t>
+  </si>
+  <si>
+    <t>Nhân viên(Reception/admin) tồn tại trong DB, hotel_id=NULL</t>
+  </si>
+  <si>
+    <t>hotelId=null</t>
+  </si>
+  <si>
+    <t>Cột KS hiện" Vui lòng cập nhật!"</t>
+  </si>
+  <si>
+    <t>STF08</t>
+  </si>
+  <si>
+    <t>Cập nhật NV hợp lệ</t>
+  </si>
+  <si>
+    <t>NV tồn tại</t>
+  </si>
+  <si>
+    <t>PUT /api/admin/staff/:id</t>
+  </si>
+  <si>
+    <t>id=1, fullName=Tên mới</t>
+  </si>
+  <si>
+    <t>STF09</t>
+  </si>
+  <si>
+    <t>Cập nhật - trùng email</t>
+  </si>
+  <si>
+    <t>email=x@test.com</t>
+  </si>
+  <si>
+    <t>Email mới đã bị trùng!</t>
+  </si>
+  <si>
+    <t>STF10</t>
+  </si>
+  <si>
+    <t>Cập nhật - trùng SĐT</t>
+  </si>
+  <si>
+    <t>phone=0909999999</t>
+  </si>
+  <si>
+    <t>Số điện thoại mới đã bị trùng!</t>
+  </si>
+  <si>
+    <t>STF11</t>
+  </si>
+  <si>
+    <t>Cập nhật NV không tồn tại</t>
+  </si>
+  <si>
+    <t>PUT /api/admin/users/9999</t>
+  </si>
+  <si>
+    <t>Không tìm thấy nhân viên!</t>
+  </si>
+  <si>
+    <t>STF12</t>
+  </si>
+  <si>
+    <t>Xóa NV</t>
+  </si>
+  <si>
+    <t>DELETE /api/admin/users/:id</t>
+  </si>
+  <si>
+    <t>Xóa NV thành công</t>
+  </si>
+  <si>
+    <t>STF13</t>
+  </si>
+  <si>
+    <t>Tìm kiếm theo tên/email</t>
+  </si>
+  <si>
+    <t>searchTerm=Nguyen</t>
+  </si>
+  <si>
+    <t>Hiện NV chứa "Nguyen" trong tên hoặc email</t>
+  </si>
+  <si>
+    <t>HOTEL01</t>
+  </si>
+  <si>
+    <t>Hotel</t>
+  </si>
+  <si>
+    <t>Xem danh sách khách sạn</t>
+  </si>
+  <si>
+    <t>KS tồn tại trong DB</t>
+  </si>
+  <si>
+    <t>GET /api/admin/hotels</t>
+  </si>
+  <si>
+    <t>Hiển thị danh sách khách sạn</t>
+  </si>
+  <si>
+    <t>HOTEL02</t>
+  </si>
+  <si>
+    <t>Thêm KS hợp lệ</t>
+  </si>
+  <si>
+    <t>POST /api/admin/hotels</t>
+  </si>
+  <si>
+    <t>name=Hotel ABC, city=HCM, address=123 Nguyễn Huệ</t>
+  </si>
+  <si>
+    <t>Tạo KS thành công
+Khách sạn=Hotel ABC; Thành phố=HCM;Địa chỉ=123 Nguyễn Huệ</t>
+  </si>
+  <si>
+    <t>HOTEL03</t>
+  </si>
+  <si>
+    <t>Thêm KS - thiếu thông tin bắt buộc</t>
+  </si>
+  <si>
+    <t>name=null, city=null</t>
+  </si>
+  <si>
+    <t>Vui lòng nhập đầy đủ thông tin bắt buộc!</t>
+  </si>
+  <si>
+    <t>HOTEL04</t>
+  </si>
+  <si>
+    <t>Thêm KS - trùng tất cả thông tin bắt buộc</t>
+  </si>
+  <si>
+    <t>Đã tồn tại KS: "Green Oasis Hanoi", HN, 15 Lý Thường Kiệt</t>
+  </si>
+  <si>
+    <t>name=Green Oasis Hanoi, city=Hà Nội, address=15 Lý Thường Kiệt</t>
+  </si>
+  <si>
+    <t>Khách sạn này đã tồn tại trên hệ thống!</t>
+  </si>
+  <si>
+    <t>HOTEL05</t>
+  </si>
+  <si>
+    <t>Thêm KS - không trùng tất cả thông tin bắt buộc</t>
+  </si>
+  <si>
+    <t>name=Green Oasis Hanoi 01, city=Hà Nội, address=15 Nguyễn Tri Phương</t>
+  </si>
+  <si>
+    <t>Tạo KS thành công</t>
+  </si>
+  <si>
+    <t>HOTEL06</t>
+  </si>
+  <si>
+    <t>Cập nhật KS hợp lệ</t>
+  </si>
+  <si>
+    <t>PUT /api/admin/hotels/:id</t>
+  </si>
+  <si>
+    <t>id=5, description="Khu du lịch"</t>
+  </si>
+  <si>
+    <t>HOTEL07</t>
+  </si>
+  <si>
+    <t>Cập nhật KS - thông tin cập nhật trùng</t>
+  </si>
+  <si>
+    <t>"Green Oasis Hanoi", HN, 15 Lý Thường Kiệt
+"Hotel ABC";HCM;123 Nguyễn Huệ (cập nhật)</t>
+  </si>
+  <si>
+    <t>"Green Oasis Hanoi", HN, 15 Lý Thường Kiệt
+"Green Oasis Hanoi", HN, 15 Lý Thường Kiệt</t>
+  </si>
+  <si>
+    <t>Thông tin cập nhật bị trùng với một khách sạn khác!</t>
+  </si>
+  <si>
+    <t>HOTEL08</t>
+  </si>
+  <si>
+    <t>Cập nhật KS không tồn tại</t>
+  </si>
+  <si>
+    <t>PUT /api/admin/hotels</t>
+  </si>
+  <si>
+    <t>Không tìm thấy khách sạn!</t>
+  </si>
+  <si>
+    <t>HOTEL09</t>
+  </si>
+  <si>
+    <t>Xóa KS — phòng đều trống</t>
+  </si>
+  <si>
+    <t>KS có phòng status=AVAILABLE</t>
+  </si>
+  <si>
+    <t>DELETE /api/admin/hotels/:id</t>
+  </si>
+  <si>
+    <t>ID=4 &amp; status của phòng=AVAILABLE</t>
+  </si>
+  <si>
+    <t>HOTEL10</t>
+  </si>
+  <si>
+    <t>Xóa KS — có phòng bận</t>
+  </si>
+  <si>
+    <t>KS có phòng status≠AVAILABLE</t>
+  </si>
+  <si>
+    <t>ID=4 &amp; status của phòng≠AVAILABLE</t>
+  </si>
+  <si>
+    <t>Không thể xóa khách sạn vì đang có phòng có khách ở hoặc đang được đặt!</t>
+  </si>
+  <si>
+    <t>HOTEL11</t>
+  </si>
+  <si>
+    <t>Xóa KS — không có phòng</t>
+  </si>
+  <si>
+    <t>Chưa có phòng gán vào khách sạn</t>
+  </si>
+  <si>
+    <t>ID=6</t>
+  </si>
+  <si>
+    <t>HOTEL12</t>
+  </si>
+  <si>
+    <t>Tìm kiếm KS theo tên</t>
+  </si>
+  <si>
+    <t>searchTerm=Green</t>
+  </si>
+  <si>
+    <t>Chỉ hiện KS chứa "Green"</t>
+  </si>
+  <si>
+    <t>HOTEL13</t>
+  </si>
+  <si>
+    <t>Lọc KS theo thành phố</t>
+  </si>
+  <si>
+    <t>chọn dropdown TP</t>
+  </si>
+  <si>
+    <t>selectedCity=Hà Nội</t>
+  </si>
+  <si>
+    <t>Chỉ hiện KS ở thành phố "Hà Nội"</t>
+  </si>
+  <si>
+    <t>Customer-Booking</t>
+  </si>
+  <si>
+    <t>1. POST /public/bookings</t>
+  </si>
+  <si>
+    <t>1. POST /public/booking trùng</t>
+  </si>
+  <si>
+    <t>Lấy booking theo id hợp lệ</t>
+  </si>
+  <si>
+    <t>1. GET /public/bookings/{id}</t>
+  </si>
+  <si>
+    <t>Trả về thông tin booking</t>
+  </si>
+  <si>
+    <t>Booking không tồn tại</t>
+  </si>
+  <si>
+    <t>Lỗi hoặc 404</t>
+  </si>
+  <si>
+    <t>ID không hợp lệ</t>
+  </si>
+  <si>
+    <t>id=abc</t>
+  </si>
+  <si>
+    <t>Gửi thông tin tới backend để tạo booking</t>
+  </si>
+  <si>
+    <t>Phòng AVAILABLE</t>
+  </si>
+  <si>
+    <t>POST /api/public/bookings</t>
+  </si>
+  <si>
+    <t>{ userId: 1, roomId: 1, checkIn: "2026-05-10", checkOut: "2026-05-12" }</t>
+  </si>
+  <si>
+    <t>Backend tạo booking mới và gửi về frontend đường link tới thanh toán VNPAY</t>
+  </si>
+  <si>
+    <t>Reception-Booking</t>
+  </si>
+  <si>
+    <t>Tạo booking hợp lệ (lễ tân đặt cho khách)</t>
+  </si>
+  <si>
+    <t>POST /api/reception/bookings</t>
+  </si>
+  <si>
+    <t>roomId=10, checkIn=+1d, checkOut=+3d</t>
+  </si>
+  <si>
+    <t>201; booking=PENDING; phòng→RESERVED</t>
+  </si>
+  <si>
+    <t>Reject — phòng không AVAILABLE</t>
+  </si>
+  <si>
+    <t>Phòng OCCUPIED/RESERVED/CLEANING/MAINTENANCE</t>
+  </si>
+  <si>
+    <t>status phòng ≠ AVAILABLE</t>
+  </si>
+  <si>
+    <t>400 — Room is not available for booking</t>
+  </si>
+  <si>
+    <t>BOOK07</t>
+  </si>
+  <si>
+    <t>Validation ngày check-in/out</t>
+  </si>
+  <si>
+    <t>POST với date sai</t>
+  </si>
+  <si>
+    <t>checkIn=yesterday / checkOut ≤ checkIn</t>
+  </si>
+  <si>
+    <t>400 — Check-in cannot be in the past / Check-out must be after check-in</t>
+  </si>
+  <si>
+    <t>BOOK08</t>
+  </si>
+  <si>
+    <t>Confirm booking PENDING</t>
+  </si>
+  <si>
+    <t>Booking=PENDING</t>
+  </si>
+  <si>
+    <t>POST /api/reception/bookings/{id}/confirm</t>
+  </si>
+  <si>
+    <t>bookingId của PENDING</t>
+  </si>
+  <si>
+    <t>200; booking=CONFIRMED; room không đổi (vẫn RESERVED)</t>
+  </si>
+  <si>
+    <t>BOOK09</t>
+  </si>
+  <si>
+    <t>Reject confirm — không phải PENDING</t>
+  </si>
+  <si>
+    <t>Booking CONFIRMED/CHECKED_IN/COMPLETED/CANCELLED</t>
+  </si>
+  <si>
+    <t>POST /{id}/confirm</t>
+  </si>
+  <si>
+    <t>status sai</t>
+  </si>
+  <si>
+    <t>400 — Only PENDING bookings can be confirmed</t>
+  </si>
+  <si>
+    <t>BOOK10</t>
+  </si>
+  <si>
+    <t>Cancel — restore room status đúng</t>
+  </si>
+  <si>
+    <t>Booking PENDING/CONFIRMED/CHECKED_IN</t>
+  </si>
+  <si>
+    <t>POST /api/reception/bookings/{id}/cancel</t>
+  </si>
+  <si>
+    <t>status PENDING/CONFIRMED --&gt; cancel;
+status CHECKED_IN --&gt; cancel</t>
+  </si>
+  <si>
+    <t>200; booking=CANCELLED; room→AVAILABLE (PENDING/CONFIRMED)
+hoặc room→CLEANING (CHECKED_IN)</t>
+  </si>
+  <si>
+    <t>BOOK11</t>
+  </si>
+  <si>
+    <t>Reject cancel COMPLETED/CANCELLED</t>
+  </si>
+  <si>
+    <t>Booking đã COMPLETED hoặc CANCELLED</t>
+  </si>
+  <si>
+    <t>POST /{id}/cancel</t>
+  </si>
+  <si>
+    <t>status=COMPLETED</t>
+  </si>
+  <si>
+    <t>400 — Cannot cancel a booking that is COMPLETED/CANCELLED</t>
+  </si>
+  <si>
+    <t>BOOK12</t>
+  </si>
+  <si>
+    <t>Lấy danh sách booking với filter</t>
+  </si>
+  <si>
+    <t>Có booking</t>
+  </si>
+  <si>
+    <t>GET /api/reception/bookings?hotelId=&amp;status=</t>
+  </si>
+  <si>
+    <t>filter status=CHECKED_IN</t>
+  </si>
+  <si>
+    <t>200 OK; list bookings theo filter</t>
+  </si>
+  <si>
+    <t>SER01</t>
+  </si>
+  <si>
+    <t>Service</t>
+  </si>
+  <si>
+    <t>Lấy danh sách dịch vụ</t>
+  </si>
+  <si>
+    <t>Hệ thống có dịch vụ</t>
+  </si>
+  <si>
+    <t>1. GET /public/services?hotelId=1</t>
+  </si>
+  <si>
+    <t>Trả về danh sách dịch vụ</t>
+  </si>
+  <si>
+    <t>SER02</t>
+  </si>
+  <si>
+    <t>Hotel không có dịch vụ</t>
+  </si>
+  <si>
+    <t>1. GET /public/services?hotelId=2</t>
+  </si>
+  <si>
+    <t>SER03</t>
+  </si>
+  <si>
+    <t>Thiếu hotelId</t>
+  </si>
+  <si>
+    <t>1. GET /public/services</t>
+  </si>
+  <si>
+    <t>SER04</t>
+  </si>
+  <si>
+    <t>hotelId không hợp lệ</t>
+  </si>
+  <si>
+    <t>1. GET /public/services?hotelId=abc</t>
+  </si>
+  <si>
+    <t>SER05</t>
+  </si>
+  <si>
+    <t>Thêm dịch vụ vào booking</t>
+  </si>
+  <si>
+    <t>1. POST /public/bookings/{id}/services</t>
+  </si>
+  <si>
+    <t>services=[{id:1,qty:2}]</t>
+  </si>
+  <si>
+    <t>SER06</t>
+  </si>
+  <si>
+    <t>SER07</t>
+  </si>
+  <si>
+    <t>Danh sách service rỗng</t>
+  </si>
+  <si>
+    <t>services=[]</t>
+  </si>
+  <si>
+    <t>Lỗi hoặc không thay đổi</t>
+  </si>
+  <si>
+    <t>SER08</t>
+  </si>
+  <si>
+    <t>Service không tồn tại</t>
+  </si>
+  <si>
+    <t>services=[{id:999}]</t>
+  </si>
+  <si>
+    <t>SER09</t>
+  </si>
+  <si>
+    <t>Số lượng không hợp lệ</t>
+  </si>
+  <si>
+    <t>qty=-1</t>
+  </si>
+  <si>
+    <t>Reception-Checkin</t>
+  </si>
+  <si>
+    <t>Phòng AVAILABLE hoặc RESERVED</t>
+  </si>
+  <si>
+    <t>POST /api/reception/bookings/check-in</t>
+  </si>
+  <si>
+    <t>roomId=10, checkOut=+2d, guestName=Nguyen Van A</t>
+  </si>
+  <si>
+    <t>201; booking=CHECKED_IN; phòng→OCCUPIED; tính tiền theo số đêm</t>
+  </si>
+  <si>
+    <t>Reject check-in — phòng không khả dụng</t>
+  </si>
+  <si>
+    <t>Phòng OCCUPIED/CLEANING/MAINTENANCE</t>
+  </si>
+  <si>
+    <t>status phòng ≠ AVAILABLE/RESERVED</t>
+  </si>
+  <si>
+    <t>400 — Room is not available for check-in</t>
+  </si>
+  <si>
+    <t>Reject double check-in cùng phòng</t>
+  </si>
+  <si>
+    <t>Phòng đã có booking CHECKED_IN</t>
+  </si>
+  <si>
+    <t>POST check-in lần 2 cho cùng roomId</t>
+  </si>
+  <si>
+    <t>roomId trùng</t>
+  </si>
+  <si>
+    <t>400 — Room already has an active check-in</t>
+  </si>
+  <si>
+    <t>Validation ngày trả phòng</t>
+  </si>
+  <si>
+    <t>POST check-in với checkOut sai</t>
+  </si>
+  <si>
+    <t>checkOut=today / checkOut=yesterday</t>
+  </si>
+  <si>
+    <t>400 — Check-out date must be after today</t>
+  </si>
+  <si>
+    <t>CI05</t>
+  </si>
+  <si>
+    <t>Reception-Checkout</t>
+  </si>
+  <si>
+    <t>Booking=CHECKED_IN</t>
+  </si>
+  <si>
+    <t>POST /api/reception/bookings/{id}/check-out</t>
+  </si>
+  <si>
+    <t>bookingId hợp lệ</t>
+  </si>
+  <si>
+    <t>200; booking=COMPLETED; phòng→CLEANING</t>
+  </si>
+  <si>
+    <t>CI06</t>
+  </si>
+  <si>
+    <t>Check-out cùng ngày — tối thiểu 1 đêm</t>
+  </si>
+  <si>
+    <t>Booking checkIn=today, original checkOut=+5d</t>
+  </si>
+  <si>
+    <t>POST check-out ngay trong ngày check-in</t>
+  </si>
+  <si>
+    <t>actual nights=0</t>
+  </si>
+  <si>
+    <t>200; totalPrice = basePrice × 1 (charge tối thiểu 1 đêm)</t>
+  </si>
+  <si>
+    <t>CI07</t>
+  </si>
+  <si>
+    <t>Check-out sớm — recalculate price</t>
+  </si>
+  <si>
+    <t>Booking checkIn=-2d, original checkOut=+3d</t>
+  </si>
+  <si>
+    <t>POST check-out tại ngày hiện tại</t>
+  </si>
+  <si>
+    <t>actual nights=2 (vs 5 ban đầu)</t>
+  </si>
+  <si>
+    <t>200; totalPrice = basePrice × 2 (theo đêm thực tế)</t>
+  </si>
+  <si>
+    <t>CI08</t>
+  </si>
+  <si>
+    <t>Reject check-out — booking không CHECKED_IN</t>
+  </si>
+  <si>
+    <t>Booking PENDING/CONFIRMED/COMPLETED/CANCELLED</t>
+  </si>
+  <si>
+    <t>POST check-out cho booking khác status</t>
+  </si>
+  <si>
+    <t>status=PENDING</t>
+  </si>
+  <si>
+    <t>400 — Booking is not checked in</t>
+  </si>
+  <si>
+    <t>CI09</t>
+  </si>
+  <si>
+    <t>ID 99 không có</t>
+  </si>
+  <si>
+    <t>POST /api/reception/bookings/99/check-out</t>
+  </si>
+  <si>
+    <t>bookingId=99</t>
+  </si>
+  <si>
+    <t>404 — Booking not found</t>
+  </si>
+  <si>
+    <t>CI10</t>
+  </si>
+  <si>
+    <t>Reception-Flow</t>
+  </si>
+  <si>
+    <t>Full lifecycle: Create→Confirm→CheckIn→CheckOut</t>
+  </si>
+  <si>
+    <t>Hotel/Room/RoomType setup</t>
+  </si>
+  <si>
+    <t>Lần lượt: POST /bookings → /confirm → /check-in → /check-out</t>
+  </si>
+  <si>
+    <t>1 booking xuyên 4 bước</t>
+  </si>
+  <si>
+    <t>Mỗi bước thành công; 
+room: AVAILABLE→RESERVED→OCCUPIED→CLEANING;
+booking: PENDING→CONFIRMED→CHECKED_IN→COMPLETED</t>
+  </si>
+  <si>
+    <t>Tạo payment thành công</t>
+  </si>
+  <si>
+    <t>1. POST /public/payment</t>
+  </si>
+  <si>
+    <t>bookingId=1, amount=100000</t>
+  </si>
+  <si>
+    <t>Trả về URL VNPay (text)</t>
+  </si>
+  <si>
+    <t>Số tiền không hợp lệ</t>
+  </si>
+  <si>
+    <t>amount=-100</t>
+  </si>
+  <si>
+    <t>bookingId=999</t>
+  </si>
+  <si>
+    <t>PAY05</t>
+  </si>
+  <si>
+    <t>Gọi api thanh toán vnpay</t>
+  </si>
+  <si>
+    <t>Sau khi booking thành công</t>
+  </si>
+  <si>
+    <t>GET api/public/payment/vnpay</t>
+  </si>
+  <si>
+    <t>bookingId=33</t>
+  </si>
+  <si>
+    <t>Trả về đường link vnpay để thanh toán</t>
+  </si>
+  <si>
+    <t>PAY06</t>
+  </si>
+  <si>
+    <t>1. GET /public/payment/vnpay</t>
+  </si>
+  <si>
+    <t>PAY07</t>
+  </si>
+  <si>
+    <t>CUS01</t>
+  </si>
+  <si>
+    <t>Filter</t>
+  </si>
+  <si>
+    <t>Sắp xếp danh sách phòng từ giá thấp đến cao (asc)</t>
+  </si>
+  <si>
+    <t>Đã đăng nhập</t>
+  </si>
+  <si>
+    <t>Bấm vào nút thấp đến cao</t>
+  </si>
+  <si>
+    <t>order = "asc"</t>
+  </si>
+  <si>
+    <t>sấp xếp thành công</t>
+  </si>
+  <si>
+    <t>CUS02</t>
+  </si>
+  <si>
+    <t>Sắp xếp danh sách phòng từ giá thấp đến cao (desc)</t>
+  </si>
+  <si>
+    <t>Bấm vào nút cao đến thấp</t>
+  </si>
+  <si>
+    <t>order = "desc"</t>
+  </si>
+  <si>
+    <t>CUS03</t>
+  </si>
+  <si>
+    <t>Calendar</t>
+  </si>
+  <si>
+    <t>Chọn ngày booking</t>
+  </si>
+  <si>
+    <t>Bấm vào lịch booking.</t>
+  </si>
+  <si>
+    <t>checkIn = "2026-05-10"
+checkOut = "2026-05-12"</t>
+  </si>
+  <si>
+    <t>chọn ngày checkin và check out thành công</t>
+  </si>
+  <si>
+    <t>CUS04</t>
+  </si>
+  <si>
+    <t>Dropdown filter</t>
+  </si>
+  <si>
+    <t>Chọn loại phòng</t>
+  </si>
+  <si>
+    <t>Bấm vào ô loại phòng</t>
+  </si>
+  <si>
+    <t>roomType = "single"</t>
+  </si>
+  <si>
+    <t>Chỉ còn lại phòng loại single</t>
+  </si>
+  <si>
+    <t>CUS05</t>
+  </si>
+  <si>
+    <t>Đặt phòng nhưng không đăng nhập</t>
+  </si>
+  <si>
+    <t>Bấm vào nút Đặt Phòng</t>
+  </si>
+  <si>
+    <t>user = null</t>
+  </si>
+  <si>
+    <t>Hiện thông báo "Bạn chưa đăng nhập!"</t>
+  </si>
+  <si>
+    <t>CUS06</t>
+  </si>
+  <si>
+    <t>Đặt phòng nhưng không chọn ngày</t>
+  </si>
+  <si>
+    <t>user = { id: 1 }
+checkIn = ""
+checkOut = ""</t>
+  </si>
+  <si>
+    <t>Hiện thông báo "Vui lòng chọn ngày!"</t>
+  </si>
+  <si>
+    <t>CUS07</t>
+  </si>
+  <si>
+    <t>Đặt phòng</t>
+  </si>
+  <si>
+    <t>user = { id: 1 }
+checkIn = "2026-05-10"
+checkOut = "2026-05-12"</t>
+  </si>
+  <si>
+    <t>Booking thành công và tiến hành gọi API thanh toán.</t>
+  </si>
+  <si>
+    <t>CUS08</t>
+  </si>
+  <si>
+    <t>Booking-Management</t>
+  </si>
+  <si>
+    <t>Xem danh sách booking</t>
+  </si>
+  <si>
+    <t>Đã đăng nhập, Hệ thống có danh sách booking cho user này</t>
+  </si>
+  <si>
+    <t>Bấm vào MyBookings trên dashboard của customer</t>
+  </si>
+  <si>
+    <t>userId = 1</t>
+  </si>
+  <si>
+    <t>Hiễn thị danh sách booking thành công</t>
+  </si>
+  <si>
+    <t>CUS09</t>
+  </si>
+  <si>
+    <t>Hủy Booking</t>
+  </si>
+  <si>
+    <t>Đã đăng nhập, User đã đặt 1 phòng.</t>
+  </si>
+  <si>
+    <t>Bấm vào nút Cancel trong trang MyBookings</t>
+  </si>
+  <si>
+    <t>bookingId = 1</t>
+  </si>
+  <si>
+    <t>Hủy Booking thành công</t>
+  </si>
+  <si>
+    <t>CUS10</t>
+  </si>
+  <si>
+    <t>Cập nhật Booking</t>
+  </si>
+  <si>
+    <t>Bấm vào nút Edit trong trang MyBookings</t>
+  </si>
+  <si>
+    <t>checkIn = "2026-06-01"
+checkOut = "2026-06-05"</t>
+  </si>
+  <si>
+    <t>Cập nhật lịch booking thành công</t>
+  </si>
+  <si>
+    <t>EDGE01</t>
+  </si>
+  <si>
+    <t>Edge</t>
+  </si>
+  <si>
+    <t>1. Gọi API với token cũ</t>
+  </si>
+  <si>
+    <t>expired</t>
+  </si>
+  <si>
+    <t>EDGE02</t>
+  </si>
+  <si>
+    <t>Reception-Edge</t>
+  </si>
+  <si>
+    <t>Đặt phòng trùng</t>
+  </si>
+  <si>
+    <t>Phòng đã RESERVED</t>
+  </si>
+  <si>
+    <t>POST 2 booking cho cùng roomId</t>
+  </si>
+  <si>
+    <t>2 booking trùng phòng</t>
+  </si>
+  <si>
+    <t>Booking 1: 201; Booking 2: 400 — Room is not available. DB chỉ có 1 booking.</t>
+  </si>
+  <si>
+    <t>EDGE03</t>
+  </si>
+  <si>
+    <t>Checkin 2 lần cùng 1 phòng</t>
+  </si>
+  <si>
+    <t>Phòng đã CHECKED_IN</t>
+  </si>
+  <si>
+    <t>POST 2 check-in cho cùng roomId</t>
+  </si>
+  <si>
+    <t>2 check-in trùng phòng</t>
+  </si>
+  <si>
+    <t>Check-in 1: 201; Check-in 2: 400 — Room is OCCUPIED</t>
+  </si>
+  <si>
+    <t>EDGE04</t>
+  </si>
+  <si>
+    <t>Checkout sớm - tính lại giá tiền</t>
+  </si>
+  <si>
+    <t>Booking CHECKED_IN, original 5 đêm</t>
+  </si>
+  <si>
+    <t>Check-out cùng ngày check-in</t>
+  </si>
+  <si>
+    <t>originalCheckOut=+5d, actual=0</t>
+  </si>
+  <si>
+    <t>totalPrice = basePrice × 1 (tối thiểu 1 đêm thay vì 5)</t>
+  </si>
+  <si>
+    <t>EDGE05</t>
+  </si>
+  <si>
+    <t>Đặt lại phòng sau khi hủy</t>
+  </si>
+  <si>
+    <t>Booking 1 đã CANCELLED</t>
+  </si>
+  <si>
+    <t>Tạo booking 2 cho cùng phòng</t>
+  </si>
+  <si>
+    <t>Booking 1 PENDING→CANCELLED;
+phòng→AVAILABLE</t>
+  </si>
+  <si>
+    <t>Booking 2: 201 OK (phòng đã về AVAILABLE)</t>
+  </si>
+  <si>
+    <t>EDGE06</t>
+  </si>
+  <si>
+    <t>State machine — không skip status</t>
+  </si>
+  <si>
+    <t>Phòng OCCUPIED</t>
+  </si>
+  <si>
+    <t>PATCH OCCUPIED → AVAILABLE (skip CLEANING)</t>
+  </si>
+  <si>
+    <t>OCCUPIED → AVAILABLE</t>
+  </si>
+  <si>
+    <t>400 — Invalid transition. Bắt buộc qua CLEANING trước</t>
+  </si>
+  <si>
+    <t>1. Gọi API protected</t>
+  </si>
+  <si>
+    <t>protected token="fake"</t>
+  </si>
+  <si>
+    <t>SEC03</t>
+  </si>
+  <si>
+    <t>Có token cũ</t>
+  </si>
+  <si>
+    <t>token expired</t>
+  </si>
+  <si>
+    <t>401 refresh hoặc logout</t>
+  </si>
+  <si>
+    <t>SEC04</t>
+  </si>
+  <si>
+    <t>Token đúng</t>
+  </si>
+  <si>
+    <t>Token hợp lệ</t>
+  </si>
+  <si>
+    <t>token valid</t>
+  </si>
+  <si>
+    <t>200 OK</t>
+  </si>
+  <si>
+    <t>SEC05</t>
+  </si>
+  <si>
+    <t>User truy cập API admin</t>
+  </si>
+  <si>
+    <t>User role=Customer</t>
+  </si>
+  <si>
+    <t>1. Gọi API admin</t>
+  </si>
+  <si>
+    <t>SEC06</t>
+  </si>
+  <si>
+    <t>Lễ tân truy cập API admin</t>
+  </si>
+  <si>
+    <t>User role=Receptionist</t>
+  </si>
+  <si>
+    <t>SEC07</t>
+  </si>
+  <si>
+    <t>Admin truy cập API admin</t>
+  </si>
+  <si>
+    <t>User role=Admin</t>
+  </si>
+  <si>
+    <t>SEC08</t>
+  </si>
+  <si>
+    <t>Refresh token hợp lệ</t>
+  </si>
+  <si>
+    <t>refreshToken valid</t>
+  </si>
+  <si>
+    <t>Trả accessToken mới</t>
+  </si>
+  <si>
+    <t>SEC09</t>
+  </si>
+  <si>
+    <t>Refresh token sai</t>
+  </si>
+  <si>
+    <t>refreshToken fake</t>
+  </si>
+  <si>
+    <t>SEC10</t>
+  </si>
+  <si>
+    <t>Không có refresh token</t>
+  </si>
+  <si>
+    <t>Logout + redirect login</t>
+  </si>
+  <si>
+    <t>SEC11</t>
+  </si>
+  <si>
+    <t>Logout xóa token</t>
+  </si>
+  <si>
+    <t>User đã login</t>
+  </si>
+  <si>
+    <t>1. Logout</t>
+  </si>
+  <si>
+    <t>Token bị xóa</t>
+  </si>
+  <si>
+    <t>SEC12</t>
+  </si>
+  <si>
+    <t>Dùng token sau logout</t>
+  </si>
+  <si>
+    <t>User đã logout</t>
+  </si>
+  <si>
+    <t>token cũ</t>
+  </si>
+  <si>
+    <t>Retest bug booking đã fix</t>
+  </si>
+  <si>
+    <t>Bug booking đã được fix</t>
+  </si>
+  <si>
+    <t>1. Tạo booking 2. Thanh toán</t>
+  </si>
+  <si>
+    <t>booking hợp lệ</t>
+  </si>
+  <si>
+    <t>Không còn lỗi, booking thành công</t>
+  </si>
+  <si>
+    <t>Update room không ảnh hưởng booking</t>
+  </si>
+  <si>
+    <t>Có booking tồn tại</t>
+  </si>
+  <si>
+    <t>1. Update room info</t>
+  </si>
+  <si>
+    <t>giá/phòng</t>
+  </si>
+  <si>
+    <t>Booking cũ không bị thay đổi</t>
+  </si>
+  <si>
+    <t>REG03</t>
+  </si>
+  <si>
+    <t>Đặt phòng sau khi sửa login</t>
+  </si>
+  <si>
+    <t>Hệ thống vừa sửa login</t>
+  </si>
+  <si>
+    <t>1. Login 2. Đặt phòng</t>
+  </si>
+  <si>
+    <t>REG04</t>
+  </si>
+  <si>
+    <t>Thanh toán sau khi sửa API payment</t>
+  </si>
+  <si>
+    <t>Hệ thống vừa fix payment</t>
+  </si>
+  <si>
+    <t>1. Booking 2. Thanh toán</t>
+  </si>
+  <si>
+    <t>VNPay test</t>
+  </si>
+  <si>
+    <t>Thanh toán thành công</t>
+  </si>
+  <si>
+    <t>REG05</t>
+  </si>
+  <si>
+    <t>API vẫn hoạt động sau fix auth</t>
+  </si>
+  <si>
+    <t>Auth đã chỉnh sửa</t>
+  </si>
+  <si>
+    <t>1. Gọi API profile</t>
+  </si>
+  <si>
+    <t>REG06</t>
+  </si>
+  <si>
+    <t>Refresh token sau fix interceptor</t>
+  </si>
+  <si>
+    <t>Code vừa sửa interceptor</t>
+  </si>
+  <si>
+    <t>1. Gọi API hết hạn token</t>
+  </si>
+  <si>
+    <t>Refresh thành công</t>
+  </si>
+  <si>
+    <t>REG07</t>
+  </si>
+  <si>
+    <t>Update profile không ảnh hưởng login</t>
+  </si>
+  <si>
+    <t>1. Update profile 2. Login lại</t>
+  </si>
+  <si>
+    <t>Login bình thường</t>
+  </si>
+  <si>
+    <t>REG08</t>
+  </si>
+  <si>
+    <t>Thay đổi giá không ảnh hưởng booking cũ</t>
+  </si>
+  <si>
+    <t>Đã có booking</t>
+  </si>
+  <si>
+    <t>1. Update giá phòng</t>
+  </si>
+  <si>
+    <t>Booking cũ giữ nguyên giá</t>
+  </si>
+  <si>
+    <t>REG09</t>
+  </si>
+  <si>
+    <t>Xóa phòng không ảnh hưởng booking cũ</t>
+  </si>
+  <si>
+    <t>Phòng đã có booking</t>
+  </si>
+  <si>
+    <t>1. Xóa phòng</t>
+  </si>
+  <si>
+    <t>Booking vẫn tồn tại</t>
+  </si>
+  <si>
+    <t>REG10</t>
+  </si>
+  <si>
+    <t>Review sau khi fix booking</t>
+  </si>
+  <si>
+    <t>Booking đã fix</t>
+  </si>
+  <si>
+    <t>1. Tạo review</t>
+  </si>
+  <si>
+    <t>Review thành công</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -918,13 +2628,28 @@
       <charset val="163"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="163"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -936,17 +2661,17 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
       </right>
-      <top style="thin">
-        <color indexed="64"/>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
       </top>
-      <bottom style="thin">
-        <color indexed="64"/>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
       </bottom>
       <diagonal/>
     </border>
@@ -954,13 +2679,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1264,7 +2998,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1277,7 +3011,7 @@
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1303,81 +3037,81 @@
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>133</v>
+        <v>87</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>197</v>
+        <v>151</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>198</v>
+        <v>152</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>133</v>
+        <v>87</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>199</v>
+        <v>153</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>197</v>
+        <v>151</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>200</v>
+        <v>154</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>133</v>
+        <v>87</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>201</v>
+        <v>155</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>197</v>
+        <v>151</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>202</v>
+        <v>156</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>133</v>
+        <v>87</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>12</v>
@@ -1386,90 +3120,90 @@
         <v>13</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>197</v>
+        <v>151</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>14</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>133</v>
+        <v>87</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>203</v>
+        <v>157</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>197</v>
+        <v>151</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>204</v>
+        <v>158</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>205</v>
+        <v>159</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>133</v>
+        <v>87</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>206</v>
+        <v>160</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>207</v>
+        <v>161</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>208</v>
+        <v>162</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>209</v>
+        <v>163</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>211</v>
+        <v>165</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>133</v>
+        <v>87</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>212</v>
+        <v>166</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>207</v>
+        <v>161</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>208</v>
+        <v>162</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>213</v>
+        <v>167</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>214</v>
+        <v>168</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>133</v>
+        <v>87</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>10</v>
@@ -1478,105 +3212,151 @@
         <v>13</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>208</v>
+        <v>162</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>215</v>
+        <v>169</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>216</v>
+        <v>170</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>133</v>
+        <v>87</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>217</v>
+        <v>171</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>208</v>
+        <v>162</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>200</v>
+        <v>154</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>218</v>
+        <v>172</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>133</v>
+        <v>87</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>219</v>
+        <v>173</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>220</v>
+        <v>174</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>221</v>
+        <v>175</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>222</v>
+        <v>176</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>224</v>
+        <v>178</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>133</v>
+        <v>87</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>225</v>
+        <v>179</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>220</v>
+        <v>174</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>221</v>
+        <v>175</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>226</v>
+        <v>180</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>227</v>
+        <v>181</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>133</v>
+        <v>87</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>228</v>
+        <v>182</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>221</v>
+        <v>175</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>229</v>
+        <v>183</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>70</v>
+        <v>61</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>248</v>
       </c>
     </row>
   </sheetData>
@@ -1585,9 +3365,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J7"/>
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:J11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1600,7 +3380,7 @@
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1626,142 +3406,234 @@
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" t="s">
-        <v>32</v>
-      </c>
-      <c r="F4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E5" t="s">
-        <v>37</v>
-      </c>
-      <c r="F5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G5" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" t="s">
-        <v>41</v>
-      </c>
-      <c r="D6" t="s">
-        <v>36</v>
-      </c>
-      <c r="E6" t="s">
-        <v>42</v>
-      </c>
-      <c r="F6" t="s">
-        <v>38</v>
-      </c>
-      <c r="G6" t="s">
+    <row r="2" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>672</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>674</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>676</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>677</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>679</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>680</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>681</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>683</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>684</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>685</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>686</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>687</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>689</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>692</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>693</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>695</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" t="s">
-        <v>45</v>
-      </c>
-      <c r="D7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" t="s">
-        <v>46</v>
-      </c>
-      <c r="F7" t="s">
-        <v>47</v>
-      </c>
-      <c r="G7" t="s">
-        <v>48</v>
+      <c r="C6" s="2" t="s">
+        <v>696</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>697</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>698</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>697</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>702</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>705</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>697</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>706</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>708</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>710</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>711</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>712</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>713</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>715</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>718</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>719</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>721</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>722</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>723</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>724</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>725</v>
       </c>
     </row>
   </sheetData>
@@ -1769,9 +3641,688 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:J7"/>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7432F7CD-D0D9-4FBC-ACD9-0494774313E8}">
+  <dimension ref="A1:G21"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="30.5" customWidth="1"/>
+    <col min="4" max="4" width="23.25" customWidth="1"/>
+    <col min="5" max="5" width="31" customWidth="1"/>
+    <col min="6" max="6" width="36.375" customWidth="1"/>
+    <col min="7" max="7" width="34" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="30" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C2" t="s">
+        <v>186</v>
+      </c>
+      <c r="D2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E2" t="s">
+        <v>187</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>189</v>
+      </c>
+      <c r="B3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C3" t="s">
+        <v>190</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>187</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>191</v>
+      </c>
+      <c r="B4" t="s">
+        <v>185</v>
+      </c>
+      <c r="C4" t="s">
+        <v>192</v>
+      </c>
+      <c r="D4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E4" t="s">
+        <v>193</v>
+      </c>
+      <c r="F4" t="s">
+        <v>194</v>
+      </c>
+      <c r="G4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>195</v>
+      </c>
+      <c r="B5" t="s">
+        <v>185</v>
+      </c>
+      <c r="C5" t="s">
+        <v>196</v>
+      </c>
+      <c r="D5" t="s">
+        <v>91</v>
+      </c>
+      <c r="E5" t="s">
+        <v>193</v>
+      </c>
+      <c r="F5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>197</v>
+      </c>
+      <c r="B6" t="s">
+        <v>185</v>
+      </c>
+      <c r="C6" t="s">
+        <v>198</v>
+      </c>
+      <c r="D6" t="s">
+        <v>91</v>
+      </c>
+      <c r="E6" t="s">
+        <v>193</v>
+      </c>
+      <c r="F6" t="s">
+        <v>199</v>
+      </c>
+      <c r="G6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>200</v>
+      </c>
+      <c r="B7" t="s">
+        <v>185</v>
+      </c>
+      <c r="C7" t="s">
+        <v>201</v>
+      </c>
+      <c r="D7" t="s">
+        <v>91</v>
+      </c>
+      <c r="E7" t="s">
+        <v>193</v>
+      </c>
+      <c r="F7" t="s">
+        <v>202</v>
+      </c>
+      <c r="G7" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>204</v>
+      </c>
+      <c r="B8" t="s">
+        <v>185</v>
+      </c>
+      <c r="C8" t="s">
+        <v>190</v>
+      </c>
+      <c r="D8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" t="s">
+        <v>193</v>
+      </c>
+      <c r="F8" t="s">
+        <v>205</v>
+      </c>
+      <c r="G8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>206</v>
+      </c>
+      <c r="B9" t="s">
+        <v>185</v>
+      </c>
+      <c r="C9" t="s">
+        <v>207</v>
+      </c>
+      <c r="D9" t="s">
+        <v>91</v>
+      </c>
+      <c r="E9" t="s">
+        <v>208</v>
+      </c>
+      <c r="F9" t="s">
+        <v>209</v>
+      </c>
+      <c r="G9" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>210</v>
+      </c>
+      <c r="B10" t="s">
+        <v>185</v>
+      </c>
+      <c r="C10" t="s">
+        <v>211</v>
+      </c>
+      <c r="D10" t="s">
+        <v>91</v>
+      </c>
+      <c r="E10" t="s">
+        <v>208</v>
+      </c>
+      <c r="F10" t="s">
+        <v>212</v>
+      </c>
+      <c r="G10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>213</v>
+      </c>
+      <c r="B11" t="s">
+        <v>185</v>
+      </c>
+      <c r="C11" t="s">
+        <v>214</v>
+      </c>
+      <c r="D11" t="s">
+        <v>91</v>
+      </c>
+      <c r="E11" t="s">
+        <v>208</v>
+      </c>
+      <c r="F11" t="s">
+        <v>215</v>
+      </c>
+      <c r="G11" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>216</v>
+      </c>
+      <c r="B12" t="s">
+        <v>185</v>
+      </c>
+      <c r="C12" t="s">
+        <v>171</v>
+      </c>
+      <c r="D12" t="s">
+        <v>91</v>
+      </c>
+      <c r="E12" t="s">
+        <v>208</v>
+      </c>
+      <c r="F12" t="s">
+        <v>217</v>
+      </c>
+      <c r="G12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>218</v>
+      </c>
+      <c r="B13" t="s">
+        <v>185</v>
+      </c>
+      <c r="C13" t="s">
+        <v>190</v>
+      </c>
+      <c r="D13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" t="s">
+        <v>208</v>
+      </c>
+      <c r="F13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>219</v>
+      </c>
+      <c r="B14" t="s">
+        <v>185</v>
+      </c>
+      <c r="C14" t="s">
+        <v>220</v>
+      </c>
+      <c r="D14" t="s">
+        <v>91</v>
+      </c>
+      <c r="E14" t="s">
+        <v>221</v>
+      </c>
+      <c r="F14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>222</v>
+      </c>
+      <c r="B15" t="s">
+        <v>185</v>
+      </c>
+      <c r="C15" t="s">
+        <v>223</v>
+      </c>
+      <c r="D15" t="s">
+        <v>91</v>
+      </c>
+      <c r="E15" t="s">
+        <v>221</v>
+      </c>
+      <c r="F15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>224</v>
+      </c>
+      <c r="B16" t="s">
+        <v>185</v>
+      </c>
+      <c r="C16" t="s">
+        <v>190</v>
+      </c>
+      <c r="D16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" t="s">
+        <v>221</v>
+      </c>
+      <c r="F16" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>225</v>
+      </c>
+      <c r="B17" t="s">
+        <v>185</v>
+      </c>
+      <c r="C17" t="s">
+        <v>226</v>
+      </c>
+      <c r="D17" t="s">
+        <v>91</v>
+      </c>
+      <c r="E17" t="s">
+        <v>227</v>
+      </c>
+      <c r="F17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G17" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>229</v>
+      </c>
+      <c r="B18" t="s">
+        <v>185</v>
+      </c>
+      <c r="C18" t="s">
+        <v>190</v>
+      </c>
+      <c r="D18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" t="s">
+        <v>227</v>
+      </c>
+      <c r="F18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>230</v>
+      </c>
+      <c r="B19" t="s">
+        <v>185</v>
+      </c>
+      <c r="C19" t="s">
+        <v>231</v>
+      </c>
+      <c r="D19" t="s">
+        <v>91</v>
+      </c>
+      <c r="E19" t="s">
+        <v>193</v>
+      </c>
+      <c r="F19" t="s">
+        <v>232</v>
+      </c>
+      <c r="G19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>233</v>
+      </c>
+      <c r="B20" t="s">
+        <v>185</v>
+      </c>
+      <c r="C20" t="s">
+        <v>234</v>
+      </c>
+      <c r="D20" t="s">
+        <v>91</v>
+      </c>
+      <c r="E20" t="s">
+        <v>208</v>
+      </c>
+      <c r="F20" t="s">
+        <v>235</v>
+      </c>
+      <c r="G20" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>236</v>
+      </c>
+      <c r="B21" t="s">
+        <v>185</v>
+      </c>
+      <c r="C21" t="s">
+        <v>237</v>
+      </c>
+      <c r="D21" t="s">
+        <v>78</v>
+      </c>
+      <c r="E21" t="s">
+        <v>221</v>
+      </c>
+      <c r="F21" t="s">
+        <v>238</v>
+      </c>
+      <c r="G21" t="s">
+        <v>239</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CF9872D-D42E-40AD-A548-A4163157BD3A}">
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="16.5" customWidth="1"/>
+    <col min="3" max="3" width="32.375" customWidth="1"/>
+    <col min="4" max="4" width="31.75" customWidth="1"/>
+    <col min="5" max="5" width="44" customWidth="1"/>
+    <col min="6" max="6" width="25.75" customWidth="1"/>
+    <col min="7" max="7" width="67" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>726</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>727</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>728</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>729</v>
+      </c>
+      <c r="G2" s="4">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>730</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>731</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>732</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>733</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>734</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>735</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>737</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>731</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>738</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>739</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>740</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>741</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="29.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>743</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>731</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>744</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>745</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>746</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>747</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="43.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>749</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>731</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>750</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>751</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>752</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>753</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="29.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>755</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>731</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>756</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>757</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>758</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>759</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>760</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <dimension ref="A1:J13"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1784,7 +4335,7 @@
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1810,142 +4361,280 @@
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F2" t="s">
-        <v>54</v>
-      </c>
-      <c r="G2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E3" t="s">
-        <v>59</v>
-      </c>
-      <c r="F3" t="s">
-        <v>60</v>
-      </c>
-      <c r="G3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>62</v>
-      </c>
-      <c r="B4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C4" t="s">
-        <v>63</v>
-      </c>
-      <c r="D4" t="s">
+    <row r="2" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E4" t="s">
-        <v>64</v>
-      </c>
-      <c r="F4" t="s">
-        <v>65</v>
-      </c>
-      <c r="G4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>66</v>
-      </c>
-      <c r="B5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C5" t="s">
-        <v>67</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="E2" s="2" t="s">
+        <v>761</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E5" t="s">
-        <v>68</v>
-      </c>
-      <c r="F5" t="s">
-        <v>69</v>
-      </c>
-      <c r="G5" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>71</v>
-      </c>
-      <c r="B6" t="s">
-        <v>50</v>
-      </c>
-      <c r="C6" t="s">
-        <v>72</v>
-      </c>
-      <c r="D6" t="s">
-        <v>73</v>
-      </c>
-      <c r="E6" t="s">
-        <v>74</v>
-      </c>
-      <c r="F6" t="s">
-        <v>38</v>
-      </c>
-      <c r="G6" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>76</v>
-      </c>
-      <c r="B7" t="s">
-        <v>50</v>
-      </c>
-      <c r="C7" t="s">
-        <v>77</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="G2" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E7" t="s">
-        <v>74</v>
-      </c>
-      <c r="F7" t="s">
-        <v>47</v>
-      </c>
-      <c r="G7" t="s">
-        <v>48</v>
+      <c r="E3" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>764</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>765</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>767</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>768</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>769</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>770</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>772</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>773</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>774</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>775</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>776</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>777</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>778</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>775</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>779</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>780</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>781</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>775</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>782</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>783</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>784</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>786</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>788</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>789</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>790</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>792</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>793</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>794</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>795</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>797</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>798</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>799</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>800</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -1953,9 +4642,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:J5"/>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+  <dimension ref="A1:J11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1968,7 +4657,7 @@
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1994,96 +4683,234 @@
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D2" t="s">
-        <v>81</v>
-      </c>
-      <c r="E2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F2" t="s">
+    <row r="2" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="G2" t="s">
+      <c r="B2" s="2" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+      <c r="C2" s="2" t="s">
+        <v>801</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>802</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>804</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>806</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>807</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>809</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>811</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>813</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>814</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>815</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>816</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>818</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>819</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>821</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>822</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>823</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C3" t="s">
-        <v>86</v>
-      </c>
-      <c r="D3" t="s">
-        <v>87</v>
-      </c>
-      <c r="E3" t="s">
-        <v>82</v>
-      </c>
-      <c r="F3" t="s">
-        <v>88</v>
-      </c>
-      <c r="G3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B4" t="s">
-        <v>90</v>
-      </c>
-      <c r="C4" t="s">
-        <v>91</v>
-      </c>
-      <c r="D4" t="s">
-        <v>92</v>
-      </c>
-      <c r="E4" t="s">
-        <v>93</v>
-      </c>
-      <c r="F4" t="s">
-        <v>83</v>
-      </c>
-      <c r="G4" t="s">
+    </row>
+    <row r="7" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>825</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>94</v>
-      </c>
-      <c r="B5" t="s">
-        <v>90</v>
-      </c>
-      <c r="C5" t="s">
-        <v>95</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="C7" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>827</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>828</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E5" t="s">
-        <v>93</v>
-      </c>
-      <c r="F5" t="s">
-        <v>96</v>
-      </c>
-      <c r="G5" t="s">
-        <v>70</v>
+      <c r="G7" s="2" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>830</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>831</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>832</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>834</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>835</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>836</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>837</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>839</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>840</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>841</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>842</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>844</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>845</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>846</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>847</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>848</v>
       </c>
     </row>
   </sheetData>
@@ -2091,9 +4918,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:J5"/>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:J35"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -2106,7 +4933,7 @@
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2132,96 +4959,786 @@
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C2" t="s">
-        <v>99</v>
-      </c>
-      <c r="D2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E2" t="s">
-        <v>100</v>
-      </c>
-      <c r="F2" t="s">
-        <v>101</v>
-      </c>
-      <c r="G2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>102</v>
-      </c>
-      <c r="B3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C3" t="s">
-        <v>103</v>
-      </c>
-      <c r="D3" t="s">
+    <row r="2" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E3" t="s">
-        <v>104</v>
-      </c>
-      <c r="F3" t="s">
-        <v>105</v>
-      </c>
-      <c r="G3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>106</v>
-      </c>
-      <c r="B4" t="s">
-        <v>98</v>
-      </c>
-      <c r="C4" t="s">
-        <v>107</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="E7" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E4" t="s">
-        <v>104</v>
-      </c>
-      <c r="F4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G4" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>109</v>
-      </c>
-      <c r="B5" t="s">
-        <v>98</v>
-      </c>
-      <c r="C5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D5" t="s">
-        <v>111</v>
-      </c>
-      <c r="E5" t="s">
-        <v>112</v>
-      </c>
-      <c r="F5" t="s">
-        <v>113</v>
-      </c>
-      <c r="G5" t="s">
-        <v>70</v>
+      <c r="E11" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="29.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="29.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="29.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="57.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="29.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="29.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="29.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="29.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="29.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>392</v>
       </c>
     </row>
   </sheetData>
@@ -2229,9 +5746,683 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:J21"/>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B2F9115-6830-428A-B97B-93F876FF9E4D}">
+  <dimension ref="A1:G14"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="25.625" customWidth="1"/>
+    <col min="4" max="4" width="39.875" customWidth="1"/>
+    <col min="5" max="5" width="30.875" customWidth="1"/>
+    <col min="6" max="6" width="33.25" customWidth="1"/>
+    <col min="7" max="7" width="43.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="43.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>399</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>403</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>411</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>412</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>414</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>416</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>419</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>421</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="29.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>423</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>426</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>431</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>411</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>431</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>438</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>416</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>431</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>441</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>449</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>450</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>452</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A67094CF-0E43-49D2-B598-13FBD3554D6E}">
+  <dimension ref="A1:G14"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="19.75" customWidth="1"/>
+    <col min="4" max="4" width="25.625" customWidth="1"/>
+    <col min="5" max="5" width="27.5" customWidth="1"/>
+    <col min="6" max="6" width="39.75" customWidth="1"/>
+    <col min="7" max="7" width="57.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="29.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>453</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>455</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>456</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="29.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>459</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>462</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="29.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>464</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>465</v>
+      </c>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>466</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="43.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>468</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>470</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="43.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>473</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>474</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>470</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>477</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>456</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="57.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>481</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>454</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>482</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>483</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>479</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>484</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="29.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>488</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="29.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>490</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>492</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>494</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="29.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>496</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>497</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>498</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="29.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>500</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>501</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>502</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>503</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>504</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>505</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>456</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>506</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>508</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>509</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>456</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>510</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>512</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:J17"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -2244,7 +6435,7 @@
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2270,464 +6461,372 @@
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>230</v>
-      </c>
-      <c r="B2" t="s">
-        <v>231</v>
-      </c>
-      <c r="C2" t="s">
-        <v>232</v>
-      </c>
-      <c r="D2" t="s">
-        <v>137</v>
-      </c>
-      <c r="E2" t="s">
-        <v>233</v>
-      </c>
-      <c r="F2" t="s">
+    <row r="2" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>235</v>
-      </c>
-      <c r="B3" t="s">
-        <v>231</v>
-      </c>
-      <c r="C3" t="s">
-        <v>236</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="E4" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E3" t="s">
-        <v>233</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="E5" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B4" t="s">
-        <v>231</v>
-      </c>
-      <c r="C4" t="s">
-        <v>238</v>
-      </c>
-      <c r="D4" t="s">
-        <v>137</v>
-      </c>
-      <c r="E4" t="s">
-        <v>239</v>
-      </c>
-      <c r="F4" t="s">
-        <v>240</v>
-      </c>
-      <c r="G4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>241</v>
-      </c>
-      <c r="B5" t="s">
-        <v>231</v>
-      </c>
-      <c r="C5" t="s">
-        <v>242</v>
-      </c>
-      <c r="D5" t="s">
-        <v>137</v>
-      </c>
-      <c r="E5" t="s">
-        <v>239</v>
-      </c>
-      <c r="F5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G5" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>243</v>
-      </c>
-      <c r="B6" t="s">
-        <v>231</v>
-      </c>
-      <c r="C6" t="s">
-        <v>244</v>
-      </c>
-      <c r="D6" t="s">
-        <v>137</v>
-      </c>
-      <c r="E6" t="s">
-        <v>239</v>
-      </c>
-      <c r="F6" t="s">
-        <v>245</v>
-      </c>
-      <c r="G6" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>246</v>
-      </c>
-      <c r="B7" t="s">
-        <v>231</v>
-      </c>
-      <c r="C7" t="s">
-        <v>247</v>
-      </c>
-      <c r="D7" t="s">
-        <v>137</v>
-      </c>
-      <c r="E7" t="s">
-        <v>239</v>
-      </c>
-      <c r="F7" t="s">
-        <v>248</v>
-      </c>
-      <c r="G7" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>250</v>
-      </c>
-      <c r="B8" t="s">
-        <v>231</v>
-      </c>
-      <c r="C8" t="s">
-        <v>236</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="E7" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E8" t="s">
-        <v>239</v>
-      </c>
-      <c r="F8" t="s">
-        <v>251</v>
-      </c>
-      <c r="G8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>252</v>
-      </c>
-      <c r="B9" t="s">
-        <v>231</v>
-      </c>
-      <c r="C9" t="s">
-        <v>253</v>
-      </c>
-      <c r="D9" t="s">
-        <v>137</v>
-      </c>
-      <c r="E9" t="s">
-        <v>254</v>
-      </c>
-      <c r="F9" t="s">
-        <v>255</v>
-      </c>
-      <c r="G9" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>256</v>
-      </c>
-      <c r="B10" t="s">
-        <v>231</v>
-      </c>
-      <c r="C10" t="s">
-        <v>257</v>
-      </c>
-      <c r="D10" t="s">
-        <v>137</v>
-      </c>
-      <c r="E10" t="s">
-        <v>254</v>
-      </c>
-      <c r="F10" t="s">
-        <v>258</v>
-      </c>
-      <c r="G10" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>259</v>
-      </c>
-      <c r="B11" t="s">
-        <v>231</v>
-      </c>
-      <c r="C11" t="s">
-        <v>260</v>
-      </c>
-      <c r="D11" t="s">
-        <v>137</v>
-      </c>
-      <c r="E11" t="s">
-        <v>254</v>
-      </c>
-      <c r="F11" t="s">
-        <v>261</v>
-      </c>
-      <c r="G11" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>262</v>
-      </c>
-      <c r="B12" t="s">
-        <v>231</v>
-      </c>
-      <c r="C12" t="s">
-        <v>217</v>
-      </c>
-      <c r="D12" t="s">
-        <v>137</v>
-      </c>
-      <c r="E12" t="s">
-        <v>254</v>
-      </c>
-      <c r="F12" t="s">
-        <v>263</v>
-      </c>
-      <c r="G12" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>264</v>
-      </c>
-      <c r="B13" t="s">
-        <v>231</v>
-      </c>
-      <c r="C13" t="s">
-        <v>236</v>
-      </c>
-      <c r="D13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E13" t="s">
-        <v>254</v>
-      </c>
-      <c r="F13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>265</v>
-      </c>
-      <c r="B14" t="s">
-        <v>231</v>
-      </c>
-      <c r="C14" t="s">
-        <v>266</v>
-      </c>
-      <c r="D14" t="s">
-        <v>137</v>
-      </c>
-      <c r="E14" t="s">
-        <v>267</v>
-      </c>
-      <c r="F14" t="s">
-        <v>13</v>
-      </c>
-      <c r="G14" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>268</v>
-      </c>
-      <c r="B15" t="s">
-        <v>231</v>
-      </c>
-      <c r="C15" t="s">
-        <v>269</v>
-      </c>
-      <c r="D15" t="s">
-        <v>137</v>
-      </c>
-      <c r="E15" t="s">
-        <v>267</v>
-      </c>
-      <c r="F15" t="s">
-        <v>13</v>
-      </c>
-      <c r="G15" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>270</v>
-      </c>
-      <c r="B16" t="s">
-        <v>231</v>
-      </c>
-      <c r="C16" t="s">
-        <v>236</v>
-      </c>
-      <c r="D16" t="s">
-        <v>13</v>
-      </c>
-      <c r="E16" t="s">
-        <v>267</v>
-      </c>
-      <c r="F16" t="s">
-        <v>13</v>
-      </c>
-      <c r="G16" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>271</v>
-      </c>
-      <c r="B17" t="s">
-        <v>231</v>
-      </c>
-      <c r="C17" t="s">
-        <v>272</v>
-      </c>
-      <c r="D17" t="s">
-        <v>137</v>
-      </c>
-      <c r="E17" t="s">
-        <v>273</v>
-      </c>
-      <c r="F17" t="s">
-        <v>13</v>
-      </c>
-      <c r="G17" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>275</v>
-      </c>
-      <c r="B18" t="s">
-        <v>231</v>
-      </c>
-      <c r="C18" t="s">
-        <v>236</v>
-      </c>
-      <c r="D18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E18" t="s">
-        <v>273</v>
-      </c>
-      <c r="F18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G18" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>276</v>
-      </c>
-      <c r="B19" t="s">
-        <v>231</v>
-      </c>
-      <c r="C19" t="s">
-        <v>277</v>
-      </c>
-      <c r="D19" t="s">
-        <v>137</v>
-      </c>
-      <c r="E19" t="s">
-        <v>239</v>
-      </c>
-      <c r="F19" t="s">
-        <v>278</v>
-      </c>
-      <c r="G19" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>279</v>
-      </c>
-      <c r="B20" t="s">
-        <v>231</v>
-      </c>
-      <c r="C20" t="s">
-        <v>280</v>
-      </c>
-      <c r="D20" t="s">
-        <v>137</v>
-      </c>
-      <c r="E20" t="s">
-        <v>254</v>
-      </c>
-      <c r="F20" t="s">
-        <v>281</v>
-      </c>
-      <c r="G20" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>282</v>
-      </c>
-      <c r="B21" t="s">
-        <v>231</v>
-      </c>
-      <c r="C21" t="s">
-        <v>283</v>
-      </c>
-      <c r="D21" t="s">
-        <v>114</v>
-      </c>
-      <c r="E21" t="s">
-        <v>267</v>
-      </c>
-      <c r="F21" t="s">
-        <v>284</v>
-      </c>
-      <c r="G21" t="s">
-        <v>285</v>
+      <c r="E8" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="57.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>571</v>
       </c>
     </row>
   </sheetData>
@@ -2735,7 +6834,738 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71E49DB8-3FB1-4CFB-AEC7-295A44D95728}">
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="23.5" customWidth="1"/>
+    <col min="4" max="4" width="19.5" customWidth="1"/>
+    <col min="5" max="5" width="34.375" customWidth="1"/>
+    <col min="6" max="6" width="25" customWidth="1"/>
+    <col min="7" max="7" width="31.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>572</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>573</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>575</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>578</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>573</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>579</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>580</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>581</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>573</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>582</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>583</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>584</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>573</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>585</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>586</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>587</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>573</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>588</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>589</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>590</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>591</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>573</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>519</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>589</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>592</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>573</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>593</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>589</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>594</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>596</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>573</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>597</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>589</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>598</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>599</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>573</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>600</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>589</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>601</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:J11"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="28" customWidth="1"/>
+    <col min="4" max="4" width="30.5" customWidth="1"/>
+    <col min="5" max="5" width="60" customWidth="1"/>
+    <col min="6" max="6" width="30.875" customWidth="1"/>
+    <col min="7" max="7" width="46" customWidth="1"/>
+    <col min="8" max="9" width="12" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+    </row>
+    <row r="2" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>602</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>603</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>604</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>605</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>602</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>607</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>608</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>604</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>609</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>602</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>611</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>612</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>613</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>614</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>602</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>616</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>524</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>617</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>620</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>621</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>622</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>623</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>624</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>626</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>621</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>627</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>628</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>629</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>630</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>632</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>621</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>633</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>634</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>635</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>636</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>638</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>621</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>639</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>640</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>641</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>642</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>644</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>621</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>519</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>645</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>646</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>647</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="100.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>649</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>650</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>651</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>652</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>655</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:J8"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="4" width="28" customWidth="1"/>
+    <col min="5" max="5" width="60" customWidth="1"/>
+    <col min="6" max="6" width="28" customWidth="1"/>
+    <col min="7" max="7" width="36" customWidth="1"/>
+    <col min="8" max="9" width="12" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+    </row>
+    <row r="2" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>656</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>658</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>660</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>662</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>663</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>664</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>667</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>669</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>662</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1ED523F6-31FB-4005-93D2-E64F5F663B90}">
   <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -2773,157 +7603,157 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>142</v>
+        <v>96</v>
       </c>
       <c r="B2" t="s">
-        <v>135</v>
+        <v>89</v>
       </c>
       <c r="C2" t="s">
-        <v>143</v>
+        <v>97</v>
       </c>
       <c r="D2" t="s">
-        <v>137</v>
+        <v>91</v>
       </c>
       <c r="E2" t="s">
-        <v>144</v>
+        <v>98</v>
       </c>
       <c r="F2" t="s">
-        <v>145</v>
+        <v>99</v>
       </c>
       <c r="G2" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>146</v>
+        <v>100</v>
       </c>
       <c r="B3" t="s">
-        <v>135</v>
+        <v>89</v>
       </c>
       <c r="C3" t="s">
-        <v>147</v>
+        <v>101</v>
       </c>
       <c r="D3" t="s">
-        <v>137</v>
+        <v>91</v>
       </c>
       <c r="E3" t="s">
-        <v>144</v>
+        <v>98</v>
       </c>
       <c r="F3" t="s">
-        <v>148</v>
+        <v>102</v>
       </c>
       <c r="G3" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>149</v>
+        <v>103</v>
       </c>
       <c r="B4" t="s">
-        <v>135</v>
+        <v>89</v>
       </c>
       <c r="C4" t="s">
-        <v>150</v>
+        <v>104</v>
       </c>
       <c r="D4" t="s">
-        <v>137</v>
+        <v>91</v>
       </c>
       <c r="E4" t="s">
-        <v>144</v>
+        <v>98</v>
       </c>
       <c r="F4" t="s">
-        <v>151</v>
+        <v>105</v>
       </c>
       <c r="G4" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>152</v>
+        <v>106</v>
       </c>
       <c r="B5" t="s">
-        <v>135</v>
+        <v>89</v>
       </c>
       <c r="C5" t="s">
-        <v>153</v>
+        <v>107</v>
       </c>
       <c r="D5" t="s">
-        <v>137</v>
+        <v>91</v>
       </c>
       <c r="E5" t="s">
-        <v>144</v>
+        <v>98</v>
       </c>
       <c r="F5" t="s">
-        <v>154</v>
+        <v>108</v>
       </c>
       <c r="G5" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>155</v>
+        <v>109</v>
       </c>
       <c r="B6" t="s">
-        <v>135</v>
+        <v>89</v>
       </c>
       <c r="C6" t="s">
-        <v>156</v>
+        <v>110</v>
       </c>
       <c r="D6" t="s">
-        <v>137</v>
+        <v>91</v>
       </c>
       <c r="E6" t="s">
-        <v>144</v>
+        <v>98</v>
       </c>
       <c r="F6" t="s">
-        <v>157</v>
+        <v>111</v>
       </c>
       <c r="G6" t="s">
-        <v>158</v>
+        <v>112</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>134</v>
+        <v>88</v>
       </c>
       <c r="B7" t="s">
-        <v>135</v>
+        <v>89</v>
       </c>
       <c r="C7" t="s">
-        <v>136</v>
+        <v>90</v>
       </c>
       <c r="D7" t="s">
-        <v>137</v>
+        <v>91</v>
       </c>
       <c r="E7" t="s">
-        <v>138</v>
+        <v>92</v>
       </c>
       <c r="F7" t="s">
         <v>13</v>
       </c>
       <c r="G7" t="s">
-        <v>139</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>140</v>
+        <v>94</v>
       </c>
       <c r="B8" t="s">
-        <v>135</v>
+        <v>89</v>
       </c>
       <c r="C8" t="s">
-        <v>141</v>
+        <v>95</v>
       </c>
       <c r="D8" t="s">
         <v>13</v>
       </c>
       <c r="E8" t="s">
-        <v>138</v>
+        <v>92</v>
       </c>
       <c r="F8" t="s">
         <v>13</v>
@@ -2934,65 +7764,65 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>159</v>
+        <v>113</v>
       </c>
       <c r="B9" t="s">
-        <v>135</v>
+        <v>89</v>
       </c>
       <c r="C9" t="s">
-        <v>160</v>
+        <v>114</v>
       </c>
       <c r="D9" t="s">
-        <v>137</v>
+        <v>91</v>
       </c>
       <c r="E9" t="s">
-        <v>161</v>
+        <v>115</v>
       </c>
       <c r="F9" t="s">
         <v>13</v>
       </c>
       <c r="G9" t="s">
-        <v>162</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>163</v>
+        <v>117</v>
       </c>
       <c r="B10" t="s">
-        <v>135</v>
+        <v>89</v>
       </c>
       <c r="C10" t="s">
-        <v>164</v>
+        <v>118</v>
       </c>
       <c r="D10" t="s">
-        <v>137</v>
+        <v>91</v>
       </c>
       <c r="E10" t="s">
-        <v>161</v>
+        <v>115</v>
       </c>
       <c r="F10" t="s">
         <v>13</v>
       </c>
       <c r="G10" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>166</v>
+        <v>120</v>
       </c>
       <c r="B11" t="s">
-        <v>135</v>
+        <v>89</v>
       </c>
       <c r="C11" t="s">
-        <v>141</v>
+        <v>95</v>
       </c>
       <c r="D11" t="s">
         <v>13</v>
       </c>
       <c r="E11" t="s">
-        <v>161</v>
+        <v>115</v>
       </c>
       <c r="F11" t="s">
         <v>13</v>
@@ -3003,183 +7833,183 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>167</v>
+        <v>121</v>
       </c>
       <c r="B12" t="s">
-        <v>135</v>
+        <v>89</v>
       </c>
       <c r="C12" t="s">
-        <v>168</v>
+        <v>122</v>
       </c>
       <c r="D12" t="s">
-        <v>169</v>
+        <v>123</v>
       </c>
       <c r="E12" t="s">
-        <v>170</v>
+        <v>124</v>
       </c>
       <c r="F12" t="s">
-        <v>171</v>
+        <v>125</v>
       </c>
       <c r="G12" t="s">
-        <v>162</v>
+        <v>116</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>172</v>
+        <v>126</v>
       </c>
       <c r="B13" t="s">
-        <v>135</v>
+        <v>89</v>
       </c>
       <c r="C13" t="s">
-        <v>173</v>
+        <v>127</v>
       </c>
       <c r="D13" t="s">
         <v>13</v>
       </c>
       <c r="E13" t="s">
-        <v>170</v>
+        <v>124</v>
       </c>
       <c r="F13" t="s">
-        <v>174</v>
+        <v>128</v>
       </c>
       <c r="G13" t="s">
-        <v>175</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>176</v>
+        <v>130</v>
       </c>
       <c r="B14" t="s">
-        <v>135</v>
+        <v>89</v>
       </c>
       <c r="C14" t="s">
-        <v>177</v>
+        <v>131</v>
       </c>
       <c r="D14" t="s">
-        <v>178</v>
+        <v>132</v>
       </c>
       <c r="E14" t="s">
-        <v>179</v>
+        <v>133</v>
       </c>
       <c r="F14" t="s">
-        <v>171</v>
+        <v>125</v>
       </c>
       <c r="G14" t="s">
-        <v>180</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>181</v>
+        <v>135</v>
       </c>
       <c r="B15" t="s">
-        <v>135</v>
+        <v>89</v>
       </c>
       <c r="C15" t="s">
-        <v>182</v>
+        <v>136</v>
       </c>
       <c r="D15" t="s">
         <v>13</v>
       </c>
       <c r="E15" t="s">
-        <v>179</v>
+        <v>133</v>
       </c>
       <c r="F15" t="s">
-        <v>183</v>
+        <v>137</v>
       </c>
       <c r="G15" t="s">
-        <v>184</v>
+        <v>138</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>185</v>
+        <v>139</v>
       </c>
       <c r="B16" t="s">
-        <v>135</v>
+        <v>89</v>
       </c>
       <c r="C16" t="s">
-        <v>186</v>
+        <v>140</v>
       </c>
       <c r="D16" t="s">
-        <v>187</v>
+        <v>141</v>
       </c>
       <c r="E16" t="s">
-        <v>188</v>
+        <v>142</v>
       </c>
       <c r="F16" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="G16" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>189</v>
+        <v>143</v>
       </c>
       <c r="B17" t="s">
-        <v>135</v>
+        <v>89</v>
       </c>
       <c r="C17" t="s">
-        <v>190</v>
+        <v>144</v>
       </c>
       <c r="D17" t="s">
-        <v>137</v>
+        <v>91</v>
       </c>
       <c r="E17" t="s">
-        <v>188</v>
+        <v>142</v>
       </c>
       <c r="F17" t="s">
-        <v>191</v>
+        <v>145</v>
       </c>
       <c r="G17" t="s">
-        <v>192</v>
+        <v>146</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>193</v>
+        <v>147</v>
       </c>
       <c r="B18" t="s">
-        <v>135</v>
+        <v>89</v>
       </c>
       <c r="C18" t="s">
-        <v>194</v>
+        <v>148</v>
       </c>
       <c r="D18" t="s">
         <v>13</v>
       </c>
       <c r="E18" t="s">
-        <v>188</v>
+        <v>142</v>
       </c>
       <c r="F18" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="G18" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>195</v>
+        <v>149</v>
       </c>
       <c r="B19" t="s">
-        <v>135</v>
+        <v>89</v>
       </c>
       <c r="C19" t="s">
-        <v>141</v>
+        <v>95</v>
       </c>
       <c r="D19" t="s">
         <v>13</v>
       </c>
       <c r="E19" t="s">
-        <v>188</v>
+        <v>142</v>
       </c>
       <c r="F19" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="G19" t="s">
         <v>16</v>
@@ -3189,188 +8019,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:J3"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="4" width="28" customWidth="1"/>
-    <col min="5" max="5" width="60" customWidth="1"/>
-    <col min="6" max="6" width="28" customWidth="1"/>
-    <col min="7" max="7" width="36" customWidth="1"/>
-    <col min="8" max="9" width="12" customWidth="1"/>
-    <col min="10" max="10" width="14" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10" ht="15" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>116</v>
-      </c>
-      <c r="B2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" t="s">
-        <v>117</v>
-      </c>
-      <c r="D2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" t="s">
-        <v>118</v>
-      </c>
-      <c r="F2" t="s">
-        <v>119</v>
-      </c>
-      <c r="G2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>120</v>
-      </c>
-      <c r="B3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" t="s">
-        <v>121</v>
-      </c>
-      <c r="D3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" t="s">
-        <v>118</v>
-      </c>
-      <c r="F3" t="s">
-        <v>122</v>
-      </c>
-      <c r="G3" t="s">
-        <v>115</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:J3"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="4" width="28" customWidth="1"/>
-    <col min="5" max="5" width="60" customWidth="1"/>
-    <col min="6" max="6" width="28" customWidth="1"/>
-    <col min="7" max="7" width="36" customWidth="1"/>
-    <col min="8" max="9" width="12" customWidth="1"/>
-    <col min="10" max="10" width="14" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10" ht="15" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>123</v>
-      </c>
-      <c r="B2" t="s">
-        <v>124</v>
-      </c>
-      <c r="C2" t="s">
-        <v>125</v>
-      </c>
-      <c r="D2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>129</v>
-      </c>
-      <c r="B3" t="s">
-        <v>124</v>
-      </c>
-      <c r="C3" t="s">
-        <v>130</v>
-      </c>
-      <c r="D3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" t="s">
-        <v>131</v>
-      </c>
-      <c r="F3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" t="s">
-        <v>132</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/docs/HMS_TestCases.xlsx
+++ b/docs/HMS_TestCases.xlsx
@@ -8,25 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\HOC_TAP\QL-KhachSan\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C12ACE1-99D3-47AA-9E94-43BB47E2A288}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18933472-F794-4838-B3E4-C340B83DB6AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7080" yWindow="2790" windowWidth="21600" windowHeight="11835" firstSheet="6" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7080" yWindow="2790" windowWidth="21600" windowHeight="11835" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AUTH" sheetId="1" r:id="rId1"/>
     <sheet name="ROOM" sheetId="2" r:id="rId2"/>
-    <sheet name="STAFF" sheetId="12" r:id="rId3"/>
-    <sheet name="HOTEL" sheetId="13" r:id="rId4"/>
-    <sheet name="BOOKING" sheetId="3" r:id="rId5"/>
-    <sheet name="SERVICES" sheetId="14" r:id="rId6"/>
-    <sheet name="CHECKIN" sheetId="4" r:id="rId7"/>
-    <sheet name="PAYMENT" sheetId="5" r:id="rId8"/>
-    <sheet name="REVIEW" sheetId="11" r:id="rId9"/>
-    <sheet name="CUSTOMER" sheetId="6" r:id="rId10"/>
-    <sheet name="PROFILE" sheetId="16" r:id="rId11"/>
-    <sheet name="EDGE" sheetId="17" r:id="rId12"/>
-    <sheet name="SECURITY" sheetId="9" r:id="rId13"/>
-    <sheet name="REGRESSION" sheetId="10" r:id="rId14"/>
+    <sheet name="ROOM_IMAGE" sheetId="18" r:id="rId3"/>
+    <sheet name="STAFF" sheetId="12" r:id="rId4"/>
+    <sheet name="HOTEL" sheetId="13" r:id="rId5"/>
+    <sheet name="BOOKING" sheetId="3" r:id="rId6"/>
+    <sheet name="SERVICES" sheetId="14" r:id="rId7"/>
+    <sheet name="CHECKIN" sheetId="4" r:id="rId8"/>
+    <sheet name="PAYMENT" sheetId="5" r:id="rId9"/>
+    <sheet name="REVIEW" sheetId="11" r:id="rId10"/>
+    <sheet name="CUSTOMER" sheetId="6" r:id="rId11"/>
+    <sheet name="PROFILE" sheetId="16" r:id="rId12"/>
+    <sheet name="EDGE" sheetId="17" r:id="rId13"/>
+    <sheet name="SECURITY" sheetId="9" r:id="rId14"/>
+    <sheet name="REGRESSION" sheetId="10" r:id="rId15"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1439" uniqueCount="849">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1600" uniqueCount="920">
   <si>
     <t>TC_ID</t>
   </si>
@@ -2601,6 +2602,219 @@
   </si>
   <si>
     <t>Review thành công</t>
+  </si>
+  <si>
+    <t>IMG01</t>
+  </si>
+  <si>
+    <t>Room Image</t>
+  </si>
+  <si>
+    <t>Lấy danh sách ảnh phòng</t>
+  </si>
+  <si>
+    <t>Room tồn tại</t>
+  </si>
+  <si>
+    <t>1. GET /reception/rooms/{roomId}/images</t>
+  </si>
+  <si>
+    <t>roomId=1</t>
+  </si>
+  <si>
+    <t>Trả về danh sách ảnh</t>
+  </si>
+  <si>
+    <t>IMG02</t>
+  </si>
+  <si>
+    <t>Phòng không tồn tại</t>
+  </si>
+  <si>
+    <t>roomId=999</t>
+  </si>
+  <si>
+    <t>IMG03</t>
+  </si>
+  <si>
+    <t>IMG04</t>
+  </si>
+  <si>
+    <t>Upload 1 ảnh thành công</t>
+  </si>
+  <si>
+    <t>User có quyền</t>
+  </si>
+  <si>
+    <t>1. POST upload</t>
+  </si>
+  <si>
+    <t>file jpg</t>
+  </si>
+  <si>
+    <t>Upload thành công</t>
+  </si>
+  <si>
+    <t>IMG05</t>
+  </si>
+  <si>
+    <t>Upload nhiều ảnh</t>
+  </si>
+  <si>
+    <t>files=[img1,img2]</t>
+  </si>
+  <si>
+    <t>IMG06</t>
+  </si>
+  <si>
+    <t>Thiếu file</t>
+  </si>
+  <si>
+    <t>files=[]</t>
+  </si>
+  <si>
+    <t>IMG07</t>
+  </si>
+  <si>
+    <t>File không hợp lệ</t>
+  </si>
+  <si>
+    <t>file .txt</t>
+  </si>
+  <si>
+    <t>IMG08</t>
+  </si>
+  <si>
+    <t>File quá lớn</t>
+  </si>
+  <si>
+    <t>file &gt; limit</t>
+  </si>
+  <si>
+    <t>IMG09</t>
+  </si>
+  <si>
+    <t>Có caption</t>
+  </si>
+  <si>
+    <t>caption="Room đẹp"</t>
+  </si>
+  <si>
+    <t>Lưu caption</t>
+  </si>
+  <si>
+    <t>IMG10</t>
+  </si>
+  <si>
+    <t>Không có caption</t>
+  </si>
+  <si>
+    <t>Vẫn upload thành công</t>
+  </si>
+  <si>
+    <t>IMG11</t>
+  </si>
+  <si>
+    <t>Không có quyền</t>
+  </si>
+  <si>
+    <t>User không phải lễ tân</t>
+  </si>
+  <si>
+    <t>IMG12</t>
+  </si>
+  <si>
+    <t>Set ảnh chính thành công</t>
+  </si>
+  <si>
+    <t>Ảnh tồn tại</t>
+  </si>
+  <si>
+    <t>1. PATCH /primary</t>
+  </si>
+  <si>
+    <t>roomId=1,imageId=1</t>
+  </si>
+  <si>
+    <t>Đặt thành ảnh chính</t>
+  </si>
+  <si>
+    <t>IMG13</t>
+  </si>
+  <si>
+    <t>Image không tồn tại</t>
+  </si>
+  <si>
+    <t>imageId=999</t>
+  </si>
+  <si>
+    <t>IMG14</t>
+  </si>
+  <si>
+    <t>IMG15</t>
+  </si>
+  <si>
+    <t>Cập nhật caption thành công</t>
+  </si>
+  <si>
+    <t>1. PATCH /caption</t>
+  </si>
+  <si>
+    <t>caption="New"</t>
+  </si>
+  <si>
+    <t>IMG16</t>
+  </si>
+  <si>
+    <t>Caption rỗng</t>
+  </si>
+  <si>
+    <t>caption=""</t>
+  </si>
+  <si>
+    <t>Thành công hoặc lỗi tùy rule</t>
+  </si>
+  <si>
+    <t>IMG17</t>
+  </si>
+  <si>
+    <t>IMG18</t>
+  </si>
+  <si>
+    <t>IMG19</t>
+  </si>
+  <si>
+    <t>Xóa ảnh thành công</t>
+  </si>
+  <si>
+    <t>1. DELETE /images/{id}</t>
+  </si>
+  <si>
+    <t>imageId=1</t>
+  </si>
+  <si>
+    <t>IMG20</t>
+  </si>
+  <si>
+    <t>Xóa ảnh không tồn tại</t>
+  </si>
+  <si>
+    <t>1. DELETE</t>
+  </si>
+  <si>
+    <t>IMG21</t>
+  </si>
+  <si>
+    <t>Xóa ảnh đang là primary</t>
+  </si>
+  <si>
+    <t>Ảnh là primary</t>
+  </si>
+  <si>
+    <t>Lỗi hoặc auto đổi ảnh khác</t>
+  </si>
+  <si>
+    <t>IMG22</t>
   </si>
 </sst>
 </file>
@@ -2679,7 +2893,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2696,6 +2910,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3366,6 +3581,462 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1ED523F6-31FB-4005-93D2-E64F5F663B90}">
+  <dimension ref="A1:G19"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="9.125" customWidth="1"/>
+    <col min="3" max="3" width="22.125" customWidth="1"/>
+    <col min="4" max="4" width="18.25" customWidth="1"/>
+    <col min="5" max="5" width="26.375" customWidth="1"/>
+    <col min="6" max="6" width="44" customWidth="1"/>
+    <col min="7" max="7" width="22.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="30" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E2" t="s">
+        <v>98</v>
+      </c>
+      <c r="F2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E3" t="s">
+        <v>98</v>
+      </c>
+      <c r="F3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C4" t="s">
+        <v>104</v>
+      </c>
+      <c r="D4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E4" t="s">
+        <v>98</v>
+      </c>
+      <c r="F4" t="s">
+        <v>105</v>
+      </c>
+      <c r="G4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>106</v>
+      </c>
+      <c r="B5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D5" t="s">
+        <v>91</v>
+      </c>
+      <c r="E5" t="s">
+        <v>98</v>
+      </c>
+      <c r="F5" t="s">
+        <v>108</v>
+      </c>
+      <c r="G5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>109</v>
+      </c>
+      <c r="B6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D6" t="s">
+        <v>91</v>
+      </c>
+      <c r="E6" t="s">
+        <v>98</v>
+      </c>
+      <c r="F6" t="s">
+        <v>111</v>
+      </c>
+      <c r="G6" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>88</v>
+      </c>
+      <c r="B7" t="s">
+        <v>89</v>
+      </c>
+      <c r="C7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D7" t="s">
+        <v>91</v>
+      </c>
+      <c r="E7" t="s">
+        <v>92</v>
+      </c>
+      <c r="F7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>94</v>
+      </c>
+      <c r="B8" t="s">
+        <v>89</v>
+      </c>
+      <c r="C8" t="s">
+        <v>95</v>
+      </c>
+      <c r="D8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" t="s">
+        <v>92</v>
+      </c>
+      <c r="F8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>113</v>
+      </c>
+      <c r="B9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D9" t="s">
+        <v>91</v>
+      </c>
+      <c r="E9" t="s">
+        <v>115</v>
+      </c>
+      <c r="F9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>117</v>
+      </c>
+      <c r="B10" t="s">
+        <v>89</v>
+      </c>
+      <c r="C10" t="s">
+        <v>118</v>
+      </c>
+      <c r="D10" t="s">
+        <v>91</v>
+      </c>
+      <c r="E10" t="s">
+        <v>115</v>
+      </c>
+      <c r="F10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>120</v>
+      </c>
+      <c r="B11" t="s">
+        <v>89</v>
+      </c>
+      <c r="C11" t="s">
+        <v>95</v>
+      </c>
+      <c r="D11" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" t="s">
+        <v>115</v>
+      </c>
+      <c r="F11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>121</v>
+      </c>
+      <c r="B12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C12" t="s">
+        <v>122</v>
+      </c>
+      <c r="D12" t="s">
+        <v>123</v>
+      </c>
+      <c r="E12" t="s">
+        <v>124</v>
+      </c>
+      <c r="F12" t="s">
+        <v>125</v>
+      </c>
+      <c r="G12" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>126</v>
+      </c>
+      <c r="B13" t="s">
+        <v>89</v>
+      </c>
+      <c r="C13" t="s">
+        <v>127</v>
+      </c>
+      <c r="D13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" t="s">
+        <v>124</v>
+      </c>
+      <c r="F13" t="s">
+        <v>128</v>
+      </c>
+      <c r="G13" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>130</v>
+      </c>
+      <c r="B14" t="s">
+        <v>89</v>
+      </c>
+      <c r="C14" t="s">
+        <v>131</v>
+      </c>
+      <c r="D14" t="s">
+        <v>132</v>
+      </c>
+      <c r="E14" t="s">
+        <v>133</v>
+      </c>
+      <c r="F14" t="s">
+        <v>125</v>
+      </c>
+      <c r="G14" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>135</v>
+      </c>
+      <c r="B15" t="s">
+        <v>89</v>
+      </c>
+      <c r="C15" t="s">
+        <v>136</v>
+      </c>
+      <c r="D15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" t="s">
+        <v>133</v>
+      </c>
+      <c r="F15" t="s">
+        <v>137</v>
+      </c>
+      <c r="G15" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>139</v>
+      </c>
+      <c r="B16" t="s">
+        <v>89</v>
+      </c>
+      <c r="C16" t="s">
+        <v>140</v>
+      </c>
+      <c r="D16" t="s">
+        <v>141</v>
+      </c>
+      <c r="E16" t="s">
+        <v>142</v>
+      </c>
+      <c r="F16" t="s">
+        <v>33</v>
+      </c>
+      <c r="G16" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>143</v>
+      </c>
+      <c r="B17" t="s">
+        <v>89</v>
+      </c>
+      <c r="C17" t="s">
+        <v>144</v>
+      </c>
+      <c r="D17" t="s">
+        <v>91</v>
+      </c>
+      <c r="E17" t="s">
+        <v>142</v>
+      </c>
+      <c r="F17" t="s">
+        <v>145</v>
+      </c>
+      <c r="G17" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>147</v>
+      </c>
+      <c r="B18" t="s">
+        <v>89</v>
+      </c>
+      <c r="C18" t="s">
+        <v>148</v>
+      </c>
+      <c r="D18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" t="s">
+        <v>142</v>
+      </c>
+      <c r="F18" t="s">
+        <v>40</v>
+      </c>
+      <c r="G18" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>149</v>
+      </c>
+      <c r="B19" t="s">
+        <v>89</v>
+      </c>
+      <c r="C19" t="s">
+        <v>95</v>
+      </c>
+      <c r="D19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" t="s">
+        <v>142</v>
+      </c>
+      <c r="F19" t="s">
+        <v>33</v>
+      </c>
+      <c r="G19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:J11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -3641,7 +4312,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7432F7CD-D0D9-4FBC-ACD9-0494774313E8}">
   <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -4141,7 +4812,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CF9872D-D42E-40AD-A548-A4163157BD3A}">
   <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -4320,7 +4991,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:J13"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -4642,7 +5313,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:J11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -5747,6 +6418,554 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A63AB1C-D7D0-4BD5-90B0-AC657FC5E5BF}">
+  <dimension ref="A1:G23"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="14.125" customWidth="1"/>
+    <col min="3" max="3" width="25" customWidth="1"/>
+    <col min="4" max="4" width="24.375" customWidth="1"/>
+    <col min="5" max="5" width="40.25" customWidth="1"/>
+    <col min="6" max="6" width="22.125" customWidth="1"/>
+    <col min="7" max="7" width="24.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>849</v>
+      </c>
+      <c r="B2" t="s">
+        <v>850</v>
+      </c>
+      <c r="C2" t="s">
+        <v>851</v>
+      </c>
+      <c r="D2" t="s">
+        <v>852</v>
+      </c>
+      <c r="E2" t="s">
+        <v>853</v>
+      </c>
+      <c r="F2" t="s">
+        <v>854</v>
+      </c>
+      <c r="G2" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>856</v>
+      </c>
+      <c r="B3" t="s">
+        <v>850</v>
+      </c>
+      <c r="C3" t="s">
+        <v>857</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>853</v>
+      </c>
+      <c r="F3" t="s">
+        <v>858</v>
+      </c>
+      <c r="G3" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>859</v>
+      </c>
+      <c r="B4" t="s">
+        <v>850</v>
+      </c>
+      <c r="C4" t="s">
+        <v>190</v>
+      </c>
+      <c r="D4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" t="s">
+        <v>80</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>860</v>
+      </c>
+      <c r="B5" t="s">
+        <v>850</v>
+      </c>
+      <c r="C5" t="s">
+        <v>861</v>
+      </c>
+      <c r="D5" t="s">
+        <v>862</v>
+      </c>
+      <c r="E5" t="s">
+        <v>863</v>
+      </c>
+      <c r="F5" t="s">
+        <v>864</v>
+      </c>
+      <c r="G5" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>866</v>
+      </c>
+      <c r="B6" t="s">
+        <v>850</v>
+      </c>
+      <c r="C6" t="s">
+        <v>867</v>
+      </c>
+      <c r="D6" t="s">
+        <v>862</v>
+      </c>
+      <c r="E6" t="s">
+        <v>863</v>
+      </c>
+      <c r="F6" t="s">
+        <v>868</v>
+      </c>
+      <c r="G6" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>869</v>
+      </c>
+      <c r="B7" t="s">
+        <v>850</v>
+      </c>
+      <c r="C7" t="s">
+        <v>870</v>
+      </c>
+      <c r="D7" t="s">
+        <v>862</v>
+      </c>
+      <c r="E7" t="s">
+        <v>863</v>
+      </c>
+      <c r="F7" t="s">
+        <v>871</v>
+      </c>
+      <c r="G7" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>872</v>
+      </c>
+      <c r="B8" t="s">
+        <v>850</v>
+      </c>
+      <c r="C8" t="s">
+        <v>873</v>
+      </c>
+      <c r="D8" t="s">
+        <v>862</v>
+      </c>
+      <c r="E8" t="s">
+        <v>863</v>
+      </c>
+      <c r="F8" t="s">
+        <v>874</v>
+      </c>
+      <c r="G8" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>875</v>
+      </c>
+      <c r="B9" t="s">
+        <v>850</v>
+      </c>
+      <c r="C9" t="s">
+        <v>876</v>
+      </c>
+      <c r="D9" t="s">
+        <v>862</v>
+      </c>
+      <c r="E9" t="s">
+        <v>863</v>
+      </c>
+      <c r="F9" t="s">
+        <v>877</v>
+      </c>
+      <c r="G9" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>878</v>
+      </c>
+      <c r="B10" t="s">
+        <v>850</v>
+      </c>
+      <c r="C10" t="s">
+        <v>879</v>
+      </c>
+      <c r="D10" t="s">
+        <v>862</v>
+      </c>
+      <c r="E10" t="s">
+        <v>863</v>
+      </c>
+      <c r="F10" t="s">
+        <v>880</v>
+      </c>
+      <c r="G10" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>882</v>
+      </c>
+      <c r="B11" t="s">
+        <v>850</v>
+      </c>
+      <c r="C11" t="s">
+        <v>883</v>
+      </c>
+      <c r="D11" t="s">
+        <v>862</v>
+      </c>
+      <c r="E11" t="s">
+        <v>863</v>
+      </c>
+      <c r="F11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>885</v>
+      </c>
+      <c r="B12" t="s">
+        <v>850</v>
+      </c>
+      <c r="C12" t="s">
+        <v>886</v>
+      </c>
+      <c r="D12" t="s">
+        <v>887</v>
+      </c>
+      <c r="E12" t="s">
+        <v>863</v>
+      </c>
+      <c r="F12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>888</v>
+      </c>
+      <c r="B13" t="s">
+        <v>850</v>
+      </c>
+      <c r="C13" t="s">
+        <v>889</v>
+      </c>
+      <c r="D13" t="s">
+        <v>890</v>
+      </c>
+      <c r="E13" t="s">
+        <v>891</v>
+      </c>
+      <c r="F13" t="s">
+        <v>892</v>
+      </c>
+      <c r="G13" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>894</v>
+      </c>
+      <c r="B14" t="s">
+        <v>850</v>
+      </c>
+      <c r="C14" t="s">
+        <v>895</v>
+      </c>
+      <c r="D14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" t="s">
+        <v>891</v>
+      </c>
+      <c r="F14" t="s">
+        <v>896</v>
+      </c>
+      <c r="G14" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>897</v>
+      </c>
+      <c r="B15" t="s">
+        <v>850</v>
+      </c>
+      <c r="C15" t="s">
+        <v>886</v>
+      </c>
+      <c r="D15" t="s">
+        <v>887</v>
+      </c>
+      <c r="E15" t="s">
+        <v>891</v>
+      </c>
+      <c r="F15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>898</v>
+      </c>
+      <c r="B16" t="s">
+        <v>850</v>
+      </c>
+      <c r="C16" t="s">
+        <v>899</v>
+      </c>
+      <c r="D16" t="s">
+        <v>890</v>
+      </c>
+      <c r="E16" t="s">
+        <v>900</v>
+      </c>
+      <c r="F16" t="s">
+        <v>901</v>
+      </c>
+      <c r="G16" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>902</v>
+      </c>
+      <c r="B17" t="s">
+        <v>850</v>
+      </c>
+      <c r="C17" t="s">
+        <v>903</v>
+      </c>
+      <c r="D17" t="s">
+        <v>890</v>
+      </c>
+      <c r="E17" t="s">
+        <v>900</v>
+      </c>
+      <c r="F17" t="s">
+        <v>904</v>
+      </c>
+      <c r="G17" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>906</v>
+      </c>
+      <c r="B18" t="s">
+        <v>850</v>
+      </c>
+      <c r="C18" t="s">
+        <v>895</v>
+      </c>
+      <c r="D18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" t="s">
+        <v>900</v>
+      </c>
+      <c r="F18" t="s">
+        <v>896</v>
+      </c>
+      <c r="G18" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>907</v>
+      </c>
+      <c r="B19" t="s">
+        <v>850</v>
+      </c>
+      <c r="C19" t="s">
+        <v>886</v>
+      </c>
+      <c r="D19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" t="s">
+        <v>900</v>
+      </c>
+      <c r="F19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>908</v>
+      </c>
+      <c r="B20" t="s">
+        <v>850</v>
+      </c>
+      <c r="C20" t="s">
+        <v>909</v>
+      </c>
+      <c r="D20" t="s">
+        <v>890</v>
+      </c>
+      <c r="E20" t="s">
+        <v>910</v>
+      </c>
+      <c r="F20" t="s">
+        <v>911</v>
+      </c>
+      <c r="G20" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>912</v>
+      </c>
+      <c r="B21" t="s">
+        <v>850</v>
+      </c>
+      <c r="C21" t="s">
+        <v>913</v>
+      </c>
+      <c r="D21" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" t="s">
+        <v>914</v>
+      </c>
+      <c r="F21" t="s">
+        <v>896</v>
+      </c>
+      <c r="G21" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>915</v>
+      </c>
+      <c r="B22" t="s">
+        <v>850</v>
+      </c>
+      <c r="C22" t="s">
+        <v>916</v>
+      </c>
+      <c r="D22" t="s">
+        <v>917</v>
+      </c>
+      <c r="E22" t="s">
+        <v>914</v>
+      </c>
+      <c r="F22" t="s">
+        <v>13</v>
+      </c>
+      <c r="G22" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>919</v>
+      </c>
+      <c r="B23" t="s">
+        <v>850</v>
+      </c>
+      <c r="C23" t="s">
+        <v>886</v>
+      </c>
+      <c r="D23" t="s">
+        <v>887</v>
+      </c>
+      <c r="E23" t="s">
+        <v>914</v>
+      </c>
+      <c r="F23" t="s">
+        <v>13</v>
+      </c>
+      <c r="G23" t="s">
+        <v>146</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B2F9115-6830-428A-B97B-93F876FF9E4D}">
   <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -6083,7 +7302,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A67094CF-0E43-49D2-B598-13FBD3554D6E}">
   <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -6420,7 +7639,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:J17"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -6834,7 +8053,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71E49DB8-3FB1-4CFB-AEC7-295A44D95728}">
   <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -7081,7 +8300,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:J11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -7215,7 +8434,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>620</v>
       </c>
@@ -7358,7 +8577,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:J8"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -7563,460 +8782,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1ED523F6-31FB-4005-93D2-E64F5F663B90}">
-  <dimension ref="A1:G19"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="2" max="2" width="9.125" customWidth="1"/>
-    <col min="3" max="3" width="22.125" customWidth="1"/>
-    <col min="4" max="4" width="18.25" customWidth="1"/>
-    <col min="5" max="5" width="26.375" customWidth="1"/>
-    <col min="6" max="6" width="44" customWidth="1"/>
-    <col min="7" max="7" width="22.375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" ht="30" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D2" t="s">
-        <v>91</v>
-      </c>
-      <c r="E2" t="s">
-        <v>98</v>
-      </c>
-      <c r="F2" t="s">
-        <v>99</v>
-      </c>
-      <c r="G2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>100</v>
-      </c>
-      <c r="B3" t="s">
-        <v>89</v>
-      </c>
-      <c r="C3" t="s">
-        <v>101</v>
-      </c>
-      <c r="D3" t="s">
-        <v>91</v>
-      </c>
-      <c r="E3" t="s">
-        <v>98</v>
-      </c>
-      <c r="F3" t="s">
-        <v>102</v>
-      </c>
-      <c r="G3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>103</v>
-      </c>
-      <c r="B4" t="s">
-        <v>89</v>
-      </c>
-      <c r="C4" t="s">
-        <v>104</v>
-      </c>
-      <c r="D4" t="s">
-        <v>91</v>
-      </c>
-      <c r="E4" t="s">
-        <v>98</v>
-      </c>
-      <c r="F4" t="s">
-        <v>105</v>
-      </c>
-      <c r="G4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>106</v>
-      </c>
-      <c r="B5" t="s">
-        <v>89</v>
-      </c>
-      <c r="C5" t="s">
-        <v>107</v>
-      </c>
-      <c r="D5" t="s">
-        <v>91</v>
-      </c>
-      <c r="E5" t="s">
-        <v>98</v>
-      </c>
-      <c r="F5" t="s">
-        <v>108</v>
-      </c>
-      <c r="G5" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>109</v>
-      </c>
-      <c r="B6" t="s">
-        <v>89</v>
-      </c>
-      <c r="C6" t="s">
-        <v>110</v>
-      </c>
-      <c r="D6" t="s">
-        <v>91</v>
-      </c>
-      <c r="E6" t="s">
-        <v>98</v>
-      </c>
-      <c r="F6" t="s">
-        <v>111</v>
-      </c>
-      <c r="G6" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>88</v>
-      </c>
-      <c r="B7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C7" t="s">
-        <v>90</v>
-      </c>
-      <c r="D7" t="s">
-        <v>91</v>
-      </c>
-      <c r="E7" t="s">
-        <v>92</v>
-      </c>
-      <c r="F7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>94</v>
-      </c>
-      <c r="B8" t="s">
-        <v>89</v>
-      </c>
-      <c r="C8" t="s">
-        <v>95</v>
-      </c>
-      <c r="D8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E8" t="s">
-        <v>92</v>
-      </c>
-      <c r="F8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>113</v>
-      </c>
-      <c r="B9" t="s">
-        <v>89</v>
-      </c>
-      <c r="C9" t="s">
-        <v>114</v>
-      </c>
-      <c r="D9" t="s">
-        <v>91</v>
-      </c>
-      <c r="E9" t="s">
-        <v>115</v>
-      </c>
-      <c r="F9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>117</v>
-      </c>
-      <c r="B10" t="s">
-        <v>89</v>
-      </c>
-      <c r="C10" t="s">
-        <v>118</v>
-      </c>
-      <c r="D10" t="s">
-        <v>91</v>
-      </c>
-      <c r="E10" t="s">
-        <v>115</v>
-      </c>
-      <c r="F10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>120</v>
-      </c>
-      <c r="B11" t="s">
-        <v>89</v>
-      </c>
-      <c r="C11" t="s">
-        <v>95</v>
-      </c>
-      <c r="D11" t="s">
-        <v>13</v>
-      </c>
-      <c r="E11" t="s">
-        <v>115</v>
-      </c>
-      <c r="F11" t="s">
-        <v>13</v>
-      </c>
-      <c r="G11" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>121</v>
-      </c>
-      <c r="B12" t="s">
-        <v>89</v>
-      </c>
-      <c r="C12" t="s">
-        <v>122</v>
-      </c>
-      <c r="D12" t="s">
-        <v>123</v>
-      </c>
-      <c r="E12" t="s">
-        <v>124</v>
-      </c>
-      <c r="F12" t="s">
-        <v>125</v>
-      </c>
-      <c r="G12" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>126</v>
-      </c>
-      <c r="B13" t="s">
-        <v>89</v>
-      </c>
-      <c r="C13" t="s">
-        <v>127</v>
-      </c>
-      <c r="D13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E13" t="s">
-        <v>124</v>
-      </c>
-      <c r="F13" t="s">
-        <v>128</v>
-      </c>
-      <c r="G13" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>130</v>
-      </c>
-      <c r="B14" t="s">
-        <v>89</v>
-      </c>
-      <c r="C14" t="s">
-        <v>131</v>
-      </c>
-      <c r="D14" t="s">
-        <v>132</v>
-      </c>
-      <c r="E14" t="s">
-        <v>133</v>
-      </c>
-      <c r="F14" t="s">
-        <v>125</v>
-      </c>
-      <c r="G14" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>135</v>
-      </c>
-      <c r="B15" t="s">
-        <v>89</v>
-      </c>
-      <c r="C15" t="s">
-        <v>136</v>
-      </c>
-      <c r="D15" t="s">
-        <v>13</v>
-      </c>
-      <c r="E15" t="s">
-        <v>133</v>
-      </c>
-      <c r="F15" t="s">
-        <v>137</v>
-      </c>
-      <c r="G15" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>139</v>
-      </c>
-      <c r="B16" t="s">
-        <v>89</v>
-      </c>
-      <c r="C16" t="s">
-        <v>140</v>
-      </c>
-      <c r="D16" t="s">
-        <v>141</v>
-      </c>
-      <c r="E16" t="s">
-        <v>142</v>
-      </c>
-      <c r="F16" t="s">
-        <v>33</v>
-      </c>
-      <c r="G16" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>143</v>
-      </c>
-      <c r="B17" t="s">
-        <v>89</v>
-      </c>
-      <c r="C17" t="s">
-        <v>144</v>
-      </c>
-      <c r="D17" t="s">
-        <v>91</v>
-      </c>
-      <c r="E17" t="s">
-        <v>142</v>
-      </c>
-      <c r="F17" t="s">
-        <v>145</v>
-      </c>
-      <c r="G17" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>147</v>
-      </c>
-      <c r="B18" t="s">
-        <v>89</v>
-      </c>
-      <c r="C18" t="s">
-        <v>148</v>
-      </c>
-      <c r="D18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E18" t="s">
-        <v>142</v>
-      </c>
-      <c r="F18" t="s">
-        <v>40</v>
-      </c>
-      <c r="G18" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>149</v>
-      </c>
-      <c r="B19" t="s">
-        <v>89</v>
-      </c>
-      <c r="C19" t="s">
-        <v>95</v>
-      </c>
-      <c r="D19" t="s">
-        <v>13</v>
-      </c>
-      <c r="E19" t="s">
-        <v>142</v>
-      </c>
-      <c r="F19" t="s">
-        <v>33</v>
-      </c>
-      <c r="G19" t="s">
-        <v>16</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
 </file>
--- a/docs/HMS_TestCases.xlsx
+++ b/docs/HMS_TestCases.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\HOC_TAP\QL-KhachSan\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BC5E4BD-200A-4A86-821B-91FBE3B9D7D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81EE4512-0AF2-4A59-8508-E422141C3EBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5415" yWindow="2790" windowWidth="21600" windowHeight="11835" firstSheet="7" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AUTH" sheetId="1" r:id="rId1"/>
@@ -4460,7 +4460,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="99.75" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" ht="71.25" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>92</v>
       </c>
@@ -4483,7 +4483,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="71.25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>95</v>
       </c>
@@ -4506,7 +4506,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="71.25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>98</v>
       </c>
@@ -4529,7 +4529,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="71.25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>101</v>
       </c>
@@ -4552,7 +4552,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="71.25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" ht="57" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>104</v>
       </c>
@@ -4575,7 +4575,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="57" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>85</v>
       </c>
@@ -4598,7 +4598,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="57" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>90</v>
       </c>
@@ -4621,7 +4621,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="71.25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>108</v>
       </c>
@@ -4644,7 +4644,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="71.25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>111</v>
       </c>
@@ -4667,7 +4667,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="57" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>114</v>
       </c>
@@ -4690,7 +4690,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="57" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>115</v>
       </c>
@@ -4736,7 +4736,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="71.25" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>123</v>
       </c>
